--- a/data/hex_xlsx/ASPO.HE.xlsx
+++ b/data/hex_xlsx/ASPO.HE.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="943" uniqueCount="519">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="943" uniqueCount="522">
   <si>
     <t>Company Fundamentals - Income Statement</t>
   </si>
@@ -936,6 +936,9 @@
     <t>Loans and overdraft facilities - Balancing value</t>
   </si>
   <si>
+    <t>Loans and overdraft facilities (not use)</t>
+  </si>
+  <si>
     <t>Accounts payable and other liabilities</t>
   </si>
   <si>
@@ -987,7 +990,13 @@
     <t>Total current liabilities</t>
   </si>
   <si>
+    <t>Loans and overdraft facilities LT</t>
+  </si>
+  <si>
     <t>Bonds</t>
+  </si>
+  <si>
+    <t>Loans and overdraft facilities (LT)</t>
   </si>
   <si>
     <t>Other Loans</t>
@@ -1701,7 +1710,7 @@
   <cellStyleXfs count="1">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
   </cellStyleXfs>
-  <cellXfs count="35">
+  <cellXfs count="36">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
@@ -1779,6 +1788,9 @@
     </xf>
     <xf borderId="3" fillId="0" fontId="8" numFmtId="165" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
       <alignment horizontal="left" shrinkToFit="0" vertical="center" wrapText="1"/>
+    </xf>
+    <xf borderId="3" fillId="0" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="left" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
     <xf borderId="3" fillId="3" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment horizontal="left" shrinkToFit="0" vertical="center" wrapText="1"/>
@@ -15228,20 +15240,48 @@
       <c r="G114" s="15">
         <v>340.48</v>
       </c>
-      <c r="H114" s="16"/>
-      <c r="I114" s="16"/>
-      <c r="J114" s="16"/>
-      <c r="K114" s="16"/>
-      <c r="L114" s="16"/>
-      <c r="M114" s="16"/>
-      <c r="N114" s="16"/>
-      <c r="O114" s="16"/>
-      <c r="P114" s="16"/>
-      <c r="Q114" s="16"/>
-      <c r="R114" s="16"/>
-      <c r="S114" s="16"/>
-      <c r="T114" s="16"/>
-      <c r="U114" s="16"/>
+      <c r="H114" s="15">
+        <v>572.28</v>
+      </c>
+      <c r="I114" s="15">
+        <v>282.63</v>
+      </c>
+      <c r="J114" s="15">
+        <v>266.82</v>
+      </c>
+      <c r="K114" s="17">
+        <v>79.85</v>
+      </c>
+      <c r="L114" s="15">
+        <v>118.28</v>
+      </c>
+      <c r="M114" s="15">
+        <v>432.38</v>
+      </c>
+      <c r="N114" s="15">
+        <v>374.35</v>
+      </c>
+      <c r="O114" s="15">
+        <v>410.16</v>
+      </c>
+      <c r="P114" s="17">
+        <v>67.49</v>
+      </c>
+      <c r="Q114" s="17">
+        <v>77.12</v>
+      </c>
+      <c r="R114" s="15">
+        <v>182.64</v>
+      </c>
+      <c r="S114" s="15">
+        <v>382.84</v>
+      </c>
+      <c r="T114" s="15">
+        <v>135.7</v>
+      </c>
+      <c r="U114" s="17">
+        <v>84.42</v>
+      </c>
       <c r="V114" s="16"/>
       <c r="W114" s="16"/>
     </row>
@@ -15480,8 +15520,8 @@
       <c r="W120" s="16"/>
     </row>
     <row r="121" ht="15.0" customHeight="1">
-      <c r="A121" s="14" t="s">
-        <v>298</v>
+      <c r="A121" s="26" t="s">
+        <v>305</v>
       </c>
       <c r="B121" s="16"/>
       <c r="C121" s="16"/>
@@ -15509,8 +15549,8 @@
       <c r="W121" s="16"/>
     </row>
     <row r="122" ht="15.0" customHeight="1">
-      <c r="A122" s="14" t="s">
-        <v>298</v>
+      <c r="A122" s="26" t="s">
+        <v>305</v>
       </c>
       <c r="B122" s="16"/>
       <c r="C122" s="16"/>
@@ -15633,7 +15673,7 @@
     </row>
     <row r="125" ht="15.0" customHeight="1">
       <c r="A125" s="14" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="B125" s="15">
         <v>777.36</v>
@@ -15688,7 +15728,7 @@
     </row>
     <row r="126" ht="15.0" customHeight="1">
       <c r="A126" s="14" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="B126" s="16"/>
       <c r="C126" s="15">
@@ -15747,7 +15787,7 @@
     </row>
     <row r="127" ht="15.0" customHeight="1">
       <c r="A127" s="14" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="B127" s="16"/>
       <c r="C127" s="16"/>
@@ -15780,7 +15820,7 @@
     </row>
     <row r="128" ht="15.0" customHeight="1">
       <c r="A128" s="14" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="B128" s="16"/>
       <c r="C128" s="17">
@@ -15841,7 +15881,7 @@
     </row>
     <row r="129" ht="15.0" customHeight="1">
       <c r="A129" s="14" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="B129" s="16"/>
       <c r="C129" s="15">
@@ -15888,7 +15928,7 @@
     </row>
     <row r="130" ht="15.0" customHeight="1">
       <c r="A130" s="14" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="B130" s="16"/>
       <c r="C130" s="17">
@@ -15945,7 +15985,7 @@
     </row>
     <row r="131" ht="15.0" customHeight="1">
       <c r="A131" s="14" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="B131" s="16"/>
       <c r="C131" s="17">
@@ -15978,7 +16018,7 @@
     </row>
     <row r="132" ht="15.0" customHeight="1">
       <c r="A132" s="14" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="B132" s="16"/>
       <c r="C132" s="17">
@@ -16042,7 +16082,7 @@
     </row>
     <row r="134" ht="15.0" customHeight="1">
       <c r="A134" s="14" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="B134" s="16"/>
       <c r="C134" s="17">
@@ -16085,7 +16125,7 @@
     </row>
     <row r="135" ht="15.0" customHeight="1">
       <c r="A135" s="14" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="B135" s="16"/>
       <c r="C135" s="17">
@@ -16128,7 +16168,7 @@
     </row>
     <row r="136" ht="15.0" customHeight="1">
       <c r="A136" s="14" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="B136" s="16"/>
       <c r="C136" s="17">
@@ -16173,7 +16213,7 @@
     </row>
     <row r="137" ht="15.0" customHeight="1">
       <c r="A137" s="14" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="B137" s="16"/>
       <c r="C137" s="16"/>
@@ -16204,7 +16244,7 @@
     </row>
     <row r="138" ht="15.0" customHeight="1">
       <c r="A138" s="14" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="B138" s="16"/>
       <c r="C138" s="17">
@@ -16269,7 +16309,7 @@
     </row>
     <row r="139" ht="15.0" customHeight="1">
       <c r="A139" s="14" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="B139" s="16"/>
       <c r="C139" s="16"/>
@@ -16298,7 +16338,7 @@
     </row>
     <row r="140" ht="15.0" customHeight="1">
       <c r="A140" s="14" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="B140" s="15">
         <v>249.28</v>
@@ -16331,7 +16371,7 @@
     </row>
     <row r="141" ht="15.0" customHeight="1">
       <c r="A141" s="14" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="B141" s="17">
         <v>1.18</v>
@@ -16362,7 +16402,7 @@
     </row>
     <row r="142" ht="15.0" customHeight="1">
       <c r="A142" s="18" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="B142" s="19">
         <v>1632.7</v>
@@ -16432,8 +16472,8 @@
       </c>
     </row>
     <row r="143" ht="15.0" customHeight="1">
-      <c r="A143" s="14" t="s">
-        <v>298</v>
+      <c r="A143" s="26" t="s">
+        <v>323</v>
       </c>
       <c r="B143" s="15">
         <v>2294.28</v>
@@ -16570,7 +16610,7 @@
     </row>
     <row r="146" ht="15.0" customHeight="1">
       <c r="A146" s="14" t="s">
-        <v>322</v>
+        <v>324</v>
       </c>
       <c r="B146" s="16"/>
       <c r="C146" s="16"/>
@@ -16722,8 +16762,8 @@
       <c r="W148" s="16"/>
     </row>
     <row r="149" ht="15.0" customHeight="1">
-      <c r="A149" s="14" t="s">
-        <v>298</v>
+      <c r="A149" s="26" t="s">
+        <v>325</v>
       </c>
       <c r="B149" s="16"/>
       <c r="C149" s="16"/>
@@ -16813,7 +16853,7 @@
     </row>
     <row r="151" ht="15.0" customHeight="1">
       <c r="A151" s="14" t="s">
-        <v>323</v>
+        <v>326</v>
       </c>
       <c r="B151" s="16"/>
       <c r="C151" s="16"/>
@@ -16846,7 +16886,7 @@
     </row>
     <row r="152" ht="15.0" customHeight="1">
       <c r="A152" s="14" t="s">
-        <v>324</v>
+        <v>327</v>
       </c>
       <c r="B152" s="15">
         <v>137.04</v>
@@ -16946,7 +16986,7 @@
     </row>
     <row r="154" ht="15.0" customHeight="1">
       <c r="A154" s="14" t="s">
-        <v>325</v>
+        <v>328</v>
       </c>
       <c r="B154" s="16"/>
       <c r="C154" s="16"/>
@@ -16977,7 +17017,7 @@
     </row>
     <row r="155" ht="15.0" customHeight="1">
       <c r="A155" s="14" t="s">
-        <v>326</v>
+        <v>329</v>
       </c>
       <c r="B155" s="16"/>
       <c r="C155" s="16"/>
@@ -17012,7 +17052,7 @@
     </row>
     <row r="156" ht="15.0" customHeight="1">
       <c r="A156" s="14" t="s">
-        <v>327</v>
+        <v>330</v>
       </c>
       <c r="B156" s="16"/>
       <c r="C156" s="16"/>
@@ -17049,7 +17089,7 @@
     </row>
     <row r="157" ht="15.0" customHeight="1">
       <c r="A157" s="14" t="s">
-        <v>328</v>
+        <v>331</v>
       </c>
       <c r="B157" s="16"/>
       <c r="C157" s="15">
@@ -17114,7 +17154,7 @@
     </row>
     <row r="158" ht="15.0" customHeight="1">
       <c r="A158" s="14" t="s">
-        <v>329</v>
+        <v>332</v>
       </c>
       <c r="B158" s="16"/>
       <c r="C158" s="16"/>
@@ -17209,7 +17249,7 @@
     </row>
     <row r="161" ht="15.0" customHeight="1">
       <c r="A161" s="14" t="s">
-        <v>330</v>
+        <v>333</v>
       </c>
       <c r="B161" s="16"/>
       <c r="C161" s="16"/>
@@ -17240,7 +17280,7 @@
     </row>
     <row r="162" ht="15.0" customHeight="1">
       <c r="A162" s="14" t="s">
-        <v>331</v>
+        <v>334</v>
       </c>
       <c r="B162" s="16"/>
       <c r="C162" s="16"/>
@@ -17269,7 +17309,7 @@
     </row>
     <row r="163" ht="15.0" customHeight="1">
       <c r="A163" s="14" t="s">
-        <v>332</v>
+        <v>335</v>
       </c>
       <c r="B163" s="21">
         <v>-1.18</v>
@@ -17304,7 +17344,7 @@
     </row>
     <row r="164" ht="15.0" customHeight="1">
       <c r="A164" s="18" t="s">
-        <v>333</v>
+        <v>336</v>
       </c>
       <c r="B164" s="19">
         <v>2502.21</v>
@@ -17375,7 +17415,7 @@
     </row>
     <row r="165" ht="15.0" customHeight="1">
       <c r="A165" s="14" t="s">
-        <v>334</v>
+        <v>337</v>
       </c>
       <c r="B165" s="16"/>
       <c r="C165" s="21">
@@ -17410,7 +17450,7 @@
     </row>
     <row r="166" ht="15.0" customHeight="1">
       <c r="A166" s="18" t="s">
-        <v>335</v>
+        <v>338</v>
       </c>
       <c r="B166" s="19">
         <v>4134.9</v>
@@ -17481,7 +17521,7 @@
     </row>
     <row r="167" ht="15.0" customHeight="1">
       <c r="A167" s="14" t="s">
-        <v>336</v>
+        <v>339</v>
       </c>
       <c r="B167" s="15">
         <v>259.91</v>
@@ -17552,7 +17592,7 @@
     </row>
     <row r="168" ht="15.0" customHeight="1">
       <c r="A168" s="14" t="s">
-        <v>337</v>
+        <v>340</v>
       </c>
       <c r="B168" s="15">
         <v>1435.4</v>
@@ -17603,7 +17643,7 @@
     </row>
     <row r="169" ht="15.0" customHeight="1">
       <c r="A169" s="14" t="s">
-        <v>338</v>
+        <v>341</v>
       </c>
       <c r="B169" s="16"/>
       <c r="C169" s="16"/>
@@ -17662,7 +17702,7 @@
     </row>
     <row r="170" ht="15.0" customHeight="1">
       <c r="A170" s="14" t="s">
-        <v>339</v>
+        <v>342</v>
       </c>
       <c r="B170" s="16"/>
       <c r="C170" s="16"/>
@@ -17719,7 +17759,7 @@
     </row>
     <row r="171" ht="15.0" customHeight="1">
       <c r="A171" s="14" t="s">
-        <v>340</v>
+        <v>343</v>
       </c>
       <c r="B171" s="16"/>
       <c r="C171" s="15">
@@ -17782,7 +17822,7 @@
     </row>
     <row r="172" ht="15.0" customHeight="1">
       <c r="A172" s="14" t="s">
-        <v>341</v>
+        <v>344</v>
       </c>
       <c r="B172" s="16"/>
       <c r="C172" s="15">
@@ -17833,7 +17873,7 @@
     </row>
     <row r="173" ht="15.0" customHeight="1">
       <c r="A173" s="14" t="s">
-        <v>342</v>
+        <v>345</v>
       </c>
       <c r="B173" s="16"/>
       <c r="C173" s="16"/>
@@ -17943,7 +17983,7 @@
     </row>
     <row r="175" ht="15.0" customHeight="1">
       <c r="A175" s="14" t="s">
-        <v>343</v>
+        <v>346</v>
       </c>
       <c r="B175" s="16"/>
       <c r="C175" s="15">
@@ -18008,7 +18048,7 @@
     </row>
     <row r="176" ht="15.0" customHeight="1">
       <c r="A176" s="14" t="s">
-        <v>344</v>
+        <v>347</v>
       </c>
       <c r="B176" s="16"/>
       <c r="C176" s="16"/>
@@ -18053,7 +18093,7 @@
     </row>
     <row r="177" ht="15.0" customHeight="1">
       <c r="A177" s="14" t="s">
-        <v>345</v>
+        <v>348</v>
       </c>
       <c r="B177" s="16"/>
       <c r="C177" s="21">
@@ -18082,7 +18122,7 @@
     </row>
     <row r="178" ht="15.0" customHeight="1">
       <c r="A178" s="18" t="s">
-        <v>346</v>
+        <v>349</v>
       </c>
       <c r="B178" s="19">
         <v>1695.31</v>
@@ -18153,7 +18193,7 @@
     </row>
     <row r="179" ht="15.0" customHeight="1">
       <c r="A179" s="14" t="s">
-        <v>347</v>
+        <v>350</v>
       </c>
       <c r="B179" s="15">
         <v>236.28</v>
@@ -18204,7 +18244,7 @@
     </row>
     <row r="180" ht="15.0" customHeight="1">
       <c r="A180" s="18" t="s">
-        <v>348</v>
+        <v>351</v>
       </c>
       <c r="B180" s="19">
         <v>236.28</v>
@@ -18255,7 +18295,7 @@
     </row>
     <row r="181" ht="15.0" customHeight="1">
       <c r="A181" s="14" t="s">
-        <v>349</v>
+        <v>352</v>
       </c>
       <c r="B181" s="16"/>
       <c r="C181" s="21">
@@ -18284,7 +18324,7 @@
     </row>
     <row r="182" ht="15.0" customHeight="1">
       <c r="A182" s="18" t="s">
-        <v>350</v>
+        <v>353</v>
       </c>
       <c r="B182" s="19">
         <v>1931.59</v>
@@ -18355,7 +18395,7 @@
     </row>
     <row r="183" ht="15.0" customHeight="1">
       <c r="A183" s="14" t="s">
-        <v>351</v>
+        <v>354</v>
       </c>
       <c r="B183" s="16"/>
       <c r="C183" s="17">
@@ -18390,7 +18430,7 @@
     </row>
     <row r="184" ht="15.0" customHeight="1">
       <c r="A184" s="18" t="s">
-        <v>352</v>
+        <v>355</v>
       </c>
       <c r="B184" s="19">
         <v>6066.49</v>
@@ -18461,7 +18501,7 @@
     </row>
     <row r="185" ht="15.0" customHeight="1">
       <c r="A185" s="14" t="s">
-        <v>353</v>
+        <v>356</v>
       </c>
       <c r="B185" s="17">
         <v>31.32</v>
@@ -18532,7 +18572,7 @@
     </row>
     <row r="186" ht="15.0" customHeight="1">
       <c r="A186" s="14" t="s">
-        <v>354</v>
+        <v>357</v>
       </c>
       <c r="B186" s="17">
         <v>0.1</v>
@@ -18603,7 +18643,7 @@
     </row>
     <row r="187" ht="15.0" customHeight="1">
       <c r="A187" s="14" t="s">
-        <v>355</v>
+        <v>358</v>
       </c>
       <c r="B187" s="17">
         <v>31.42</v>
@@ -18674,7 +18714,7 @@
     </row>
     <row r="188" ht="15.0" customHeight="1">
       <c r="A188" s="14" t="s">
-        <v>356</v>
+        <v>359</v>
       </c>
       <c r="B188" s="16"/>
       <c r="C188" s="16"/>
@@ -18717,7 +18757,7 @@
     </row>
     <row r="189" ht="15.0" customHeight="1">
       <c r="A189" s="14" t="s">
-        <v>357</v>
+        <v>360</v>
       </c>
       <c r="B189" s="16"/>
       <c r="C189" s="16"/>
@@ -18780,7 +18820,7 @@
     </row>
     <row r="190" ht="15.0" customHeight="1">
       <c r="A190" s="14" t="s">
-        <v>358</v>
+        <v>361</v>
       </c>
       <c r="B190" s="16"/>
       <c r="C190" s="16"/>
@@ -18825,7 +18865,7 @@
     </row>
     <row r="191" ht="15.0" customHeight="1">
       <c r="A191" s="14" t="s">
-        <v>359</v>
+        <v>362</v>
       </c>
       <c r="B191" s="16"/>
       <c r="C191" s="16"/>
@@ -18870,7 +18910,7 @@
     </row>
     <row r="192" ht="15.0" customHeight="1">
       <c r="A192" s="14" t="s">
-        <v>360</v>
+        <v>363</v>
       </c>
       <c r="B192" s="16"/>
       <c r="C192" s="16"/>
@@ -18915,7 +18955,7 @@
     </row>
     <row r="193" ht="15.0" customHeight="1">
       <c r="A193" s="14" t="s">
-        <v>361</v>
+        <v>364</v>
       </c>
       <c r="B193" s="16"/>
       <c r="C193" s="16"/>
@@ -18944,7 +18984,7 @@
     </row>
     <row r="194" ht="15.0" customHeight="1">
       <c r="A194" s="14" t="s">
-        <v>362</v>
+        <v>365</v>
       </c>
       <c r="B194" s="16"/>
       <c r="C194" s="16"/>
@@ -18975,7 +19015,7 @@
     </row>
     <row r="195" ht="15.0" customHeight="1">
       <c r="A195" s="14" t="s">
-        <v>363</v>
+        <v>366</v>
       </c>
       <c r="B195" s="16"/>
       <c r="C195" s="16"/>
@@ -19022,7 +19062,7 @@
     </row>
     <row r="196" ht="15.0" customHeight="1">
       <c r="A196" s="14" t="s">
-        <v>364</v>
+        <v>367</v>
       </c>
       <c r="B196" s="16"/>
       <c r="C196" s="16"/>
@@ -19051,7 +19091,7 @@
     </row>
     <row r="197" ht="15.0" customHeight="1">
       <c r="A197" s="14" t="s">
-        <v>365</v>
+        <v>368</v>
       </c>
       <c r="B197" s="16"/>
       <c r="C197" s="15">
@@ -19116,7 +19156,7 @@
     </row>
     <row r="198" ht="15.0" customHeight="1">
       <c r="A198" s="14" t="s">
-        <v>366</v>
+        <v>369</v>
       </c>
       <c r="B198" s="16"/>
       <c r="C198" s="17">
@@ -19159,7 +19199,7 @@
     </row>
     <row r="199" ht="15.0" customHeight="1">
       <c r="A199" s="14" t="s">
-        <v>367</v>
+        <v>370</v>
       </c>
       <c r="B199" s="16"/>
       <c r="C199" s="17">
@@ -19202,7 +19242,7 @@
     </row>
     <row r="200" ht="15.0" customHeight="1">
       <c r="A200" s="14" t="s">
-        <v>368</v>
+        <v>371</v>
       </c>
       <c r="B200" s="16"/>
       <c r="C200" s="17">
@@ -19245,7 +19285,7 @@
     </row>
     <row r="201" ht="15.0" customHeight="1">
       <c r="A201" s="14" t="s">
-        <v>369</v>
+        <v>372</v>
       </c>
       <c r="B201" s="16"/>
       <c r="C201" s="17">
@@ -19290,7 +19330,7 @@
     </row>
     <row r="202" ht="15.0" customHeight="1">
       <c r="A202" s="14" t="s">
-        <v>370</v>
+        <v>373</v>
       </c>
       <c r="B202" s="16"/>
       <c r="C202" s="15">
@@ -19325,7 +19365,7 @@
     </row>
     <row r="203" ht="15.0" customHeight="1">
       <c r="A203" s="14" t="s">
-        <v>371</v>
+        <v>374</v>
       </c>
       <c r="B203" s="16"/>
       <c r="C203" s="16"/>
@@ -19362,7 +19402,7 @@
     </row>
     <row r="204" ht="15.0" customHeight="1">
       <c r="A204" s="14" t="s">
-        <v>372</v>
+        <v>375</v>
       </c>
       <c r="B204" s="16"/>
       <c r="C204" s="16"/>
@@ -19397,7 +19437,7 @@
     </row>
     <row r="205" ht="15.0" customHeight="1">
       <c r="A205" s="14" t="s">
-        <v>373</v>
+        <v>376</v>
       </c>
       <c r="B205" s="16"/>
       <c r="C205" s="16"/>
@@ -19460,7 +19500,7 @@
     </row>
     <row r="206" ht="15.0" customHeight="1">
       <c r="A206" s="14" t="s">
-        <v>374</v>
+        <v>377</v>
       </c>
       <c r="B206" s="16"/>
       <c r="C206" s="15">
@@ -19525,7 +19565,7 @@
     </row>
     <row r="207" ht="15.0" customHeight="1">
       <c r="A207" s="14" t="s">
-        <v>375</v>
+        <v>378</v>
       </c>
       <c r="B207" s="16"/>
       <c r="C207" s="15">
@@ -19590,7 +19630,7 @@
     </row>
     <row r="208" ht="15.0" customHeight="1">
       <c r="A208" s="14" t="s">
-        <v>376</v>
+        <v>379</v>
       </c>
       <c r="B208" s="16"/>
       <c r="C208" s="15">
@@ -19655,7 +19695,7 @@
     </row>
     <row r="209" ht="15.0" customHeight="1">
       <c r="A209" s="14" t="s">
-        <v>377</v>
+        <v>380</v>
       </c>
       <c r="B209" s="16"/>
       <c r="C209" s="15">
@@ -19718,7 +19758,7 @@
     </row>
     <row r="210" ht="15.0" customHeight="1">
       <c r="A210" s="14" t="s">
-        <v>378</v>
+        <v>381</v>
       </c>
       <c r="B210" s="17">
         <v>31.32</v>
@@ -19789,7 +19829,7 @@
     </row>
     <row r="211" ht="15.0" customHeight="1">
       <c r="A211" s="14" t="s">
-        <v>379</v>
+        <v>382</v>
       </c>
       <c r="B211" s="17">
         <v>0.1</v>
@@ -19860,7 +19900,7 @@
     </row>
     <row r="212" ht="15.0" customHeight="1">
       <c r="A212" s="14" t="s">
-        <v>380</v>
+        <v>383</v>
       </c>
       <c r="B212" s="17">
         <v>31.42</v>
@@ -19931,7 +19971,7 @@
     </row>
     <row r="213" ht="15.0" customHeight="1">
       <c r="A213" s="14" t="s">
-        <v>381</v>
+        <v>384</v>
       </c>
       <c r="B213" s="17">
         <v>1.0</v>
@@ -20808,7 +20848,7 @@
   <sheetData>
     <row r="1" ht="15.0" customHeight="1">
       <c r="A1" s="1" t="s">
-        <v>382</v>
+        <v>385</v>
       </c>
       <c r="B1" s="2"/>
       <c r="C1" s="2"/>
@@ -21194,70 +21234,70 @@
         <v>44</v>
       </c>
       <c r="B15" s="10" t="s">
-        <v>383</v>
+        <v>386</v>
       </c>
       <c r="C15" s="10" t="s">
-        <v>383</v>
+        <v>386</v>
       </c>
       <c r="D15" s="10" t="s">
-        <v>383</v>
+        <v>386</v>
       </c>
       <c r="E15" s="10" t="s">
-        <v>383</v>
+        <v>386</v>
       </c>
       <c r="F15" s="10" t="s">
-        <v>383</v>
+        <v>386</v>
       </c>
       <c r="G15" s="10" t="s">
-        <v>383</v>
+        <v>386</v>
       </c>
       <c r="H15" s="10" t="s">
-        <v>383</v>
+        <v>386</v>
       </c>
       <c r="I15" s="10" t="s">
-        <v>383</v>
+        <v>386</v>
       </c>
       <c r="J15" s="10" t="s">
-        <v>383</v>
+        <v>386</v>
       </c>
       <c r="K15" s="10" t="s">
-        <v>383</v>
+        <v>386</v>
       </c>
       <c r="L15" s="10" t="s">
-        <v>383</v>
+        <v>386</v>
       </c>
       <c r="M15" s="10" t="s">
-        <v>383</v>
+        <v>386</v>
       </c>
       <c r="N15" s="10" t="s">
-        <v>383</v>
+        <v>386</v>
       </c>
       <c r="O15" s="10" t="s">
-        <v>383</v>
+        <v>386</v>
       </c>
       <c r="P15" s="10" t="s">
-        <v>383</v>
+        <v>386</v>
       </c>
       <c r="Q15" s="10" t="s">
-        <v>383</v>
+        <v>386</v>
       </c>
       <c r="R15" s="10" t="s">
-        <v>383</v>
+        <v>386</v>
       </c>
       <c r="S15" s="10" t="s">
-        <v>383</v>
+        <v>386</v>
       </c>
       <c r="T15" s="10" t="s">
-        <v>383</v>
+        <v>386</v>
       </c>
       <c r="U15" s="10" t="s">
-        <v>383</v>
+        <v>386</v>
       </c>
       <c r="V15" s="10" t="s">
-        <v>383</v>
+        <v>386</v>
       </c>
       <c r="W15" s="10" t="s">
-        <v>383</v>
+        <v>386</v>
       </c>
     </row>
     <row r="16" ht="15.0" customHeight="1" outlineLevel="1">
@@ -21333,7 +21373,7 @@
     </row>
     <row r="18">
       <c r="A18" s="12" t="s">
-        <v>384</v>
+        <v>387</v>
       </c>
       <c r="B18" s="6"/>
       <c r="C18" s="6"/>
@@ -21502,7 +21542,7 @@
     </row>
     <row r="21" ht="15.0" customHeight="1">
       <c r="A21" s="14" t="s">
-        <v>385</v>
+        <v>388</v>
       </c>
       <c r="B21" s="16"/>
       <c r="C21" s="16">
@@ -21537,7 +21577,7 @@
     </row>
     <row r="22" ht="15.0" customHeight="1">
       <c r="A22" s="14" t="s">
-        <v>386</v>
+        <v>389</v>
       </c>
       <c r="B22" s="16"/>
       <c r="C22" s="16"/>
@@ -21631,7 +21671,7 @@
     </row>
     <row r="24" ht="15.0" customHeight="1">
       <c r="A24" s="14" t="s">
-        <v>387</v>
+        <v>390</v>
       </c>
       <c r="B24" s="16"/>
       <c r="C24" s="21">
@@ -21698,7 +21738,7 @@
     </row>
     <row r="25" ht="15.0" customHeight="1">
       <c r="A25" s="14" t="s">
-        <v>388</v>
+        <v>391</v>
       </c>
       <c r="B25" s="16"/>
       <c r="C25" s="16"/>
@@ -21739,7 +21779,7 @@
     </row>
     <row r="26" ht="15.0" customHeight="1">
       <c r="A26" s="14" t="s">
-        <v>389</v>
+        <v>392</v>
       </c>
       <c r="B26" s="16"/>
       <c r="C26" s="16"/>
@@ -21817,7 +21857,7 @@
     </row>
     <row r="28" ht="15.0" customHeight="1">
       <c r="A28" s="14" t="s">
-        <v>390</v>
+        <v>393</v>
       </c>
       <c r="B28" s="16"/>
       <c r="C28" s="17">
@@ -21870,7 +21910,7 @@
     </row>
     <row r="29" ht="15.0" customHeight="1">
       <c r="A29" s="14" t="s">
-        <v>391</v>
+        <v>394</v>
       </c>
       <c r="B29" s="16"/>
       <c r="C29" s="21">
@@ -21923,7 +21963,7 @@
     </row>
     <row r="30" ht="15.0" customHeight="1">
       <c r="A30" s="14" t="s">
-        <v>392</v>
+        <v>395</v>
       </c>
       <c r="B30" s="15">
         <v>201.28</v>
@@ -21960,7 +22000,7 @@
     </row>
     <row r="31" ht="15.0" customHeight="1">
       <c r="A31" s="14" t="s">
-        <v>393</v>
+        <v>396</v>
       </c>
       <c r="B31" s="16"/>
       <c r="C31" s="17">
@@ -22009,7 +22049,7 @@
     </row>
     <row r="32" ht="15.0" customHeight="1">
       <c r="A32" s="14" t="s">
-        <v>394</v>
+        <v>397</v>
       </c>
       <c r="B32" s="16"/>
       <c r="C32" s="16"/>
@@ -22038,7 +22078,7 @@
     </row>
     <row r="33" ht="15.0" customHeight="1">
       <c r="A33" s="14" t="s">
-        <v>395</v>
+        <v>398</v>
       </c>
       <c r="B33" s="16"/>
       <c r="C33" s="21">
@@ -22067,7 +22107,7 @@
     </row>
     <row r="34" ht="15.0" customHeight="1">
       <c r="A34" s="14" t="s">
-        <v>389</v>
+        <v>392</v>
       </c>
       <c r="B34" s="16"/>
       <c r="C34" s="17">
@@ -22100,7 +22140,7 @@
     </row>
     <row r="35" ht="15.0" customHeight="1">
       <c r="A35" s="14" t="s">
-        <v>396</v>
+        <v>399</v>
       </c>
       <c r="B35" s="16"/>
       <c r="C35" s="17">
@@ -22167,7 +22207,7 @@
     </row>
     <row r="36" ht="15.0" customHeight="1">
       <c r="A36" s="14" t="s">
-        <v>397</v>
+        <v>400</v>
       </c>
       <c r="B36" s="16"/>
       <c r="C36" s="21">
@@ -22234,7 +22274,7 @@
     </row>
     <row r="37" ht="15.0" customHeight="1">
       <c r="A37" s="14" t="s">
-        <v>398</v>
+        <v>401</v>
       </c>
       <c r="B37" s="16"/>
       <c r="C37" s="17">
@@ -22267,7 +22307,7 @@
     </row>
     <row r="38" ht="15.0" customHeight="1">
       <c r="A38" s="14" t="s">
-        <v>399</v>
+        <v>402</v>
       </c>
       <c r="B38" s="15">
         <v>114.69</v>
@@ -22304,7 +22344,7 @@
     </row>
     <row r="39" ht="15.0" customHeight="1">
       <c r="A39" s="14" t="s">
-        <v>400</v>
+        <v>403</v>
       </c>
       <c r="B39" s="16"/>
       <c r="C39" s="20">
@@ -22371,7 +22411,7 @@
     </row>
     <row r="40" ht="15.0" customHeight="1">
       <c r="A40" s="14" t="s">
-        <v>401</v>
+        <v>404</v>
       </c>
       <c r="B40" s="21">
         <v>-21.06</v>
@@ -22400,7 +22440,7 @@
     </row>
     <row r="41" ht="15.0" customHeight="1">
       <c r="A41" s="14" t="s">
-        <v>402</v>
+        <v>405</v>
       </c>
       <c r="B41" s="20">
         <v>-134.58</v>
@@ -22471,7 +22511,7 @@
     </row>
     <row r="42" ht="15.0" customHeight="1">
       <c r="A42" s="14" t="s">
-        <v>403</v>
+        <v>406</v>
       </c>
       <c r="B42" s="17">
         <v>11.7</v>
@@ -22542,7 +22582,7 @@
     </row>
     <row r="43" ht="15.0" customHeight="1">
       <c r="A43" s="14" t="s">
-        <v>404</v>
+        <v>407</v>
       </c>
       <c r="B43" s="16"/>
       <c r="C43" s="16"/>
@@ -22583,7 +22623,7 @@
     </row>
     <row r="44" ht="15.0" customHeight="1">
       <c r="A44" s="14" t="s">
-        <v>405</v>
+        <v>408</v>
       </c>
       <c r="B44" s="21">
         <v>-53.83</v>
@@ -22654,7 +22694,7 @@
     </row>
     <row r="45" ht="15.0" customHeight="1">
       <c r="A45" s="14" t="s">
-        <v>406</v>
+        <v>409</v>
       </c>
       <c r="B45" s="16"/>
       <c r="C45" s="16"/>
@@ -22683,7 +22723,7 @@
     </row>
     <row r="46" ht="15.0" customHeight="1">
       <c r="A46" s="14" t="s">
-        <v>407</v>
+        <v>410</v>
       </c>
       <c r="B46" s="16"/>
       <c r="C46" s="16"/>
@@ -22712,7 +22752,7 @@
     </row>
     <row r="47" ht="15.0" customHeight="1">
       <c r="A47" s="14" t="s">
-        <v>408</v>
+        <v>411</v>
       </c>
       <c r="B47" s="16"/>
       <c r="C47" s="21">
@@ -22782,7 +22822,7 @@
     </row>
     <row r="49" ht="15.0" customHeight="1">
       <c r="A49" s="18" t="s">
-        <v>409</v>
+        <v>412</v>
       </c>
       <c r="B49" s="19">
         <v>572.26</v>
@@ -22853,7 +22893,7 @@
     </row>
     <row r="50" ht="15.0" customHeight="1">
       <c r="A50" s="14" t="s">
-        <v>410</v>
+        <v>413</v>
       </c>
       <c r="B50" s="16"/>
       <c r="C50" s="16"/>
@@ -22898,7 +22938,7 @@
     </row>
     <row r="51" ht="15.0" customHeight="1">
       <c r="A51" s="14" t="s">
-        <v>411</v>
+        <v>414</v>
       </c>
       <c r="B51" s="15">
         <v>222.35</v>
@@ -22939,7 +22979,7 @@
     </row>
     <row r="52" ht="15.0" customHeight="1">
       <c r="A52" s="14" t="s">
-        <v>412</v>
+        <v>415</v>
       </c>
       <c r="B52" s="16"/>
       <c r="C52" s="16"/>
@@ -22980,7 +23020,7 @@
     </row>
     <row r="53" ht="15.0" customHeight="1">
       <c r="A53" s="14" t="s">
-        <v>413</v>
+        <v>416</v>
       </c>
       <c r="B53" s="20">
         <v>-401.4</v>
@@ -23051,7 +23091,7 @@
     </row>
     <row r="54" ht="15.0" customHeight="1">
       <c r="A54" s="14" t="s">
-        <v>414</v>
+        <v>417</v>
       </c>
       <c r="B54" s="16"/>
       <c r="C54" s="16"/>
@@ -23108,7 +23148,7 @@
     </row>
     <row r="55" ht="15.0" customHeight="1">
       <c r="A55" s="14" t="s">
-        <v>415</v>
+        <v>418</v>
       </c>
       <c r="B55" s="16">
         <v>0.0</v>
@@ -23163,7 +23203,7 @@
     </row>
     <row r="56" ht="15.0" customHeight="1">
       <c r="A56" s="14" t="s">
-        <v>416</v>
+        <v>419</v>
       </c>
       <c r="B56" s="21">
         <v>-19.89</v>
@@ -23218,7 +23258,7 @@
     </row>
     <row r="57" ht="15.0" customHeight="1">
       <c r="A57" s="14" t="s">
-        <v>417</v>
+        <v>420</v>
       </c>
       <c r="B57" s="16"/>
       <c r="C57" s="16"/>
@@ -23257,7 +23297,7 @@
     </row>
     <row r="58" ht="15.0" customHeight="1">
       <c r="A58" s="14" t="s">
-        <v>418</v>
+        <v>421</v>
       </c>
       <c r="B58" s="16"/>
       <c r="C58" s="16">
@@ -23288,7 +23328,7 @@
     </row>
     <row r="59" ht="15.0" customHeight="1">
       <c r="A59" s="14" t="s">
-        <v>419</v>
+        <v>422</v>
       </c>
       <c r="B59" s="16"/>
       <c r="C59" s="16"/>
@@ -23337,7 +23377,7 @@
     </row>
     <row r="60" ht="15.0" customHeight="1">
       <c r="A60" s="14" t="s">
-        <v>420</v>
+        <v>423</v>
       </c>
       <c r="B60" s="16"/>
       <c r="C60" s="16"/>
@@ -23370,7 +23410,7 @@
     </row>
     <row r="61" ht="15.0" customHeight="1">
       <c r="A61" s="14" t="s">
-        <v>421</v>
+        <v>424</v>
       </c>
       <c r="B61" s="16"/>
       <c r="C61" s="20">
@@ -23399,7 +23439,7 @@
     </row>
     <row r="62" ht="15.0" customHeight="1">
       <c r="A62" s="14" t="s">
-        <v>422</v>
+        <v>425</v>
       </c>
       <c r="B62" s="16"/>
       <c r="C62" s="15">
@@ -23428,7 +23468,7 @@
     </row>
     <row r="63" ht="15.0" customHeight="1">
       <c r="A63" s="14" t="s">
-        <v>423</v>
+        <v>426</v>
       </c>
       <c r="B63" s="16"/>
       <c r="C63" s="16"/>
@@ -23465,7 +23505,7 @@
     </row>
     <row r="64" ht="15.0" customHeight="1">
       <c r="A64" s="14" t="s">
-        <v>424</v>
+        <v>427</v>
       </c>
       <c r="B64" s="16"/>
       <c r="C64" s="16"/>
@@ -23496,7 +23536,7 @@
     </row>
     <row r="65" ht="15.0" customHeight="1">
       <c r="A65" s="14" t="s">
-        <v>425</v>
+        <v>428</v>
       </c>
       <c r="B65" s="16"/>
       <c r="C65" s="16"/>
@@ -23564,7 +23604,7 @@
     </row>
     <row r="67" ht="15.0" customHeight="1">
       <c r="A67" s="14" t="s">
-        <v>401</v>
+        <v>404</v>
       </c>
       <c r="B67" s="21">
         <v>-62.02</v>
@@ -23593,7 +23633,7 @@
     </row>
     <row r="68" ht="15.0" customHeight="1">
       <c r="A68" s="14" t="s">
-        <v>426</v>
+        <v>429</v>
       </c>
       <c r="B68" s="21">
         <v>-1.17</v>
@@ -23622,7 +23662,7 @@
     </row>
     <row r="69" ht="15.0" customHeight="1">
       <c r="A69" s="18" t="s">
-        <v>427</v>
+        <v>430</v>
       </c>
       <c r="B69" s="25">
         <v>-262.14</v>
@@ -23693,7 +23733,7 @@
     </row>
     <row r="70" ht="15.0" customHeight="1">
       <c r="A70" s="14" t="s">
-        <v>428</v>
+        <v>431</v>
       </c>
       <c r="B70" s="16"/>
       <c r="C70" s="16"/>
@@ -23724,7 +23764,7 @@
     </row>
     <row r="71" ht="15.0" customHeight="1">
       <c r="A71" s="14" t="s">
-        <v>429</v>
+        <v>432</v>
       </c>
       <c r="B71" s="16"/>
       <c r="C71" s="16"/>
@@ -23767,7 +23807,7 @@
     </row>
     <row r="72" ht="15.0" customHeight="1">
       <c r="A72" s="14" t="s">
-        <v>430</v>
+        <v>433</v>
       </c>
       <c r="B72" s="16"/>
       <c r="C72" s="16"/>
@@ -23804,7 +23844,7 @@
     </row>
     <row r="73" ht="15.0" customHeight="1">
       <c r="A73" s="14" t="s">
-        <v>431</v>
+        <v>434</v>
       </c>
       <c r="B73" s="16"/>
       <c r="C73" s="16"/>
@@ -23855,7 +23895,7 @@
     </row>
     <row r="74" ht="15.0" customHeight="1">
       <c r="A74" s="14" t="s">
-        <v>432</v>
+        <v>435</v>
       </c>
       <c r="B74" s="15">
         <v>533.64</v>
@@ -23916,7 +23956,7 @@
     </row>
     <row r="75" ht="15.0" customHeight="1">
       <c r="A75" s="14" t="s">
-        <v>433</v>
+        <v>436</v>
       </c>
       <c r="B75" s="21">
         <v>-8.19</v>
@@ -23949,7 +23989,7 @@
     </row>
     <row r="76" ht="15.0" customHeight="1">
       <c r="A76" s="14" t="s">
-        <v>434</v>
+        <v>437</v>
       </c>
       <c r="B76" s="21">
         <v>-83.09</v>
@@ -24012,7 +24052,7 @@
     </row>
     <row r="77" ht="15.0" customHeight="1">
       <c r="A77" s="14" t="s">
-        <v>435</v>
+        <v>438</v>
       </c>
       <c r="B77" s="20">
         <v>-351.08</v>
@@ -24055,7 +24095,7 @@
     </row>
     <row r="78" ht="15.0" customHeight="1">
       <c r="A78" s="14" t="s">
-        <v>436</v>
+        <v>439</v>
       </c>
       <c r="B78" s="20">
         <v>-126.39</v>
@@ -24096,7 +24136,7 @@
     </row>
     <row r="79" ht="15.0" customHeight="1">
       <c r="A79" s="14" t="s">
-        <v>437</v>
+        <v>440</v>
       </c>
       <c r="B79" s="21">
         <v>-30.43</v>
@@ -24159,7 +24199,7 @@
     </row>
     <row r="80" ht="15.0" customHeight="1">
       <c r="A80" s="14" t="s">
-        <v>438</v>
+        <v>441</v>
       </c>
       <c r="B80" s="16"/>
       <c r="C80" s="16"/>
@@ -24192,7 +24232,7 @@
     </row>
     <row r="81" ht="15.0" customHeight="1">
       <c r="A81" s="14" t="s">
-        <v>439</v>
+        <v>442</v>
       </c>
       <c r="B81" s="21">
         <v>-70.22</v>
@@ -24253,7 +24293,7 @@
     </row>
     <row r="82" ht="15.0" customHeight="1">
       <c r="A82" s="14" t="s">
-        <v>440</v>
+        <v>443</v>
       </c>
       <c r="B82" s="21">
         <v>-24.58</v>
@@ -24284,7 +24324,7 @@
     </row>
     <row r="83" ht="15.0" customHeight="1">
       <c r="A83" s="14" t="s">
-        <v>432</v>
+        <v>435</v>
       </c>
       <c r="B83" s="16"/>
       <c r="C83" s="16"/>
@@ -24335,7 +24375,7 @@
     </row>
     <row r="84" ht="15.0" customHeight="1">
       <c r="A84" s="14" t="s">
-        <v>441</v>
+        <v>444</v>
       </c>
       <c r="B84" s="16"/>
       <c r="C84" s="16"/>
@@ -24366,7 +24406,7 @@
     </row>
     <row r="85" ht="15.0" customHeight="1">
       <c r="A85" s="14" t="s">
-        <v>442</v>
+        <v>445</v>
       </c>
       <c r="B85" s="16"/>
       <c r="C85" s="17">
@@ -24399,7 +24439,7 @@
     </row>
     <row r="86" ht="15.0" customHeight="1">
       <c r="A86" s="14" t="s">
-        <v>443</v>
+        <v>446</v>
       </c>
       <c r="B86" s="16"/>
       <c r="C86" s="16"/>
@@ -24430,7 +24470,7 @@
     </row>
     <row r="87" ht="15.0" customHeight="1">
       <c r="A87" s="14" t="s">
-        <v>444</v>
+        <v>447</v>
       </c>
       <c r="B87" s="16"/>
       <c r="C87" s="16"/>
@@ -24461,7 +24501,7 @@
     </row>
     <row r="88" ht="15.0" customHeight="1">
       <c r="A88" s="14" t="s">
-        <v>439</v>
+        <v>442</v>
       </c>
       <c r="B88" s="16"/>
       <c r="C88" s="16"/>
@@ -24496,7 +24536,7 @@
     </row>
     <row r="89" ht="15.0" customHeight="1">
       <c r="A89" s="14" t="s">
-        <v>445</v>
+        <v>448</v>
       </c>
       <c r="B89" s="21">
         <v>-1.17</v>
@@ -24527,7 +24567,7 @@
     </row>
     <row r="90" ht="15.0" customHeight="1">
       <c r="A90" s="14" t="s">
-        <v>443</v>
+        <v>446</v>
       </c>
       <c r="B90" s="21">
         <v>-58.51</v>
@@ -24556,7 +24596,7 @@
     </row>
     <row r="91" ht="15.0" customHeight="1">
       <c r="A91" s="14" t="s">
-        <v>446</v>
+        <v>449</v>
       </c>
       <c r="B91" s="16"/>
       <c r="C91" s="15">
@@ -24585,7 +24625,7 @@
     </row>
     <row r="92" ht="15.0" customHeight="1">
       <c r="A92" s="18" t="s">
-        <v>447</v>
+        <v>450</v>
       </c>
       <c r="B92" s="25">
         <v>-220.01</v>
@@ -24786,7 +24826,7 @@
     </row>
     <row r="95" ht="15.0" customHeight="1">
       <c r="A95" s="14" t="s">
-        <v>448</v>
+        <v>451</v>
       </c>
       <c r="B95" s="15">
         <v>519.82</v>
@@ -24857,7 +24897,7 @@
     </row>
     <row r="96" ht="15.0" customHeight="1">
       <c r="A96" s="14" t="s">
-        <v>449</v>
+        <v>452</v>
       </c>
       <c r="B96" s="17">
         <v>90.11</v>
@@ -24908,7 +24948,7 @@
     </row>
     <row r="97" ht="15.0" customHeight="1">
       <c r="A97" s="14" t="s">
-        <v>450</v>
+        <v>453</v>
       </c>
       <c r="B97" s="16"/>
       <c r="C97" s="16"/>
@@ -24939,7 +24979,7 @@
     </row>
     <row r="98" ht="15.0" customHeight="1">
       <c r="A98" s="14" t="s">
-        <v>451</v>
+        <v>454</v>
       </c>
       <c r="B98" s="16"/>
       <c r="C98" s="16"/>
@@ -24970,7 +25010,7 @@
     </row>
     <row r="99" ht="15.0" customHeight="1">
       <c r="A99" s="18" t="s">
-        <v>452</v>
+        <v>455</v>
       </c>
       <c r="B99" s="24">
         <v>88.94</v>
@@ -25041,7 +25081,7 @@
     </row>
     <row r="100" ht="15.0" customHeight="1">
       <c r="A100" s="14" t="s">
-        <v>453</v>
+        <v>456</v>
       </c>
       <c r="B100" s="15">
         <v>310.12</v>
@@ -26003,7 +26043,7 @@
   <sheetData>
     <row r="1" ht="15.0" customHeight="1">
       <c r="A1" s="1" t="s">
-        <v>454</v>
+        <v>457</v>
       </c>
       <c r="B1" s="2"/>
       <c r="C1" s="2"/>
@@ -26173,22 +26213,22 @@
         <v>39</v>
       </c>
       <c r="W11" s="7" t="s">
-        <v>455</v>
+        <v>458</v>
       </c>
       <c r="X11" s="7" t="s">
-        <v>456</v>
+        <v>459</v>
       </c>
       <c r="Y11" s="7" t="s">
-        <v>457</v>
+        <v>460</v>
       </c>
       <c r="Z11" s="7" t="s">
-        <v>458</v>
+        <v>461</v>
       </c>
       <c r="AA11" s="7" t="s">
-        <v>459</v>
+        <v>462</v>
       </c>
       <c r="AB11" s="7" t="s">
-        <v>460</v>
+        <v>463</v>
       </c>
     </row>
     <row r="12" ht="15.0" customHeight="1" outlineLevel="1">
@@ -26623,7 +26663,7 @@
     </row>
     <row r="18">
       <c r="A18" s="12" t="s">
-        <v>461</v>
+        <v>464</v>
       </c>
       <c r="B18" s="6"/>
       <c r="C18" s="6"/>
@@ -26721,3469 +26761,3469 @@
         <v>70</v>
       </c>
       <c r="W19" s="13" t="s">
-        <v>462</v>
+        <v>465</v>
       </c>
       <c r="X19" s="13" t="s">
-        <v>463</v>
+        <v>466</v>
       </c>
       <c r="Y19" s="13" t="s">
-        <v>464</v>
+        <v>467</v>
       </c>
       <c r="Z19" s="13" t="s">
-        <v>465</v>
+        <v>468</v>
       </c>
       <c r="AA19" s="13" t="s">
-        <v>466</v>
+        <v>469</v>
       </c>
       <c r="AB19" s="13" t="s">
-        <v>467</v>
+        <v>470</v>
       </c>
     </row>
     <row r="20" ht="15.0" customHeight="1">
-      <c r="A20" s="26" t="s">
-        <v>468</v>
-      </c>
-      <c r="B20" s="27"/>
-      <c r="C20" s="27"/>
-      <c r="D20" s="27"/>
-      <c r="E20" s="27"/>
-      <c r="F20" s="27"/>
-      <c r="G20" s="27"/>
-      <c r="H20" s="27"/>
-      <c r="I20" s="27"/>
-      <c r="J20" s="27"/>
-      <c r="K20" s="27"/>
-      <c r="L20" s="27"/>
-      <c r="M20" s="27"/>
-      <c r="N20" s="27"/>
-      <c r="O20" s="27"/>
-      <c r="P20" s="27"/>
-      <c r="Q20" s="27"/>
-      <c r="R20" s="27"/>
-      <c r="S20" s="27"/>
-      <c r="T20" s="27"/>
-      <c r="U20" s="27"/>
-      <c r="V20" s="27"/>
-      <c r="W20" s="27"/>
-      <c r="X20" s="27"/>
-      <c r="Y20" s="27"/>
-      <c r="Z20" s="27"/>
-      <c r="AA20" s="27"/>
-      <c r="AB20" s="27"/>
+      <c r="A20" s="27" t="s">
+        <v>471</v>
+      </c>
+      <c r="B20" s="28"/>
+      <c r="C20" s="28"/>
+      <c r="D20" s="28"/>
+      <c r="E20" s="28"/>
+      <c r="F20" s="28"/>
+      <c r="G20" s="28"/>
+      <c r="H20" s="28"/>
+      <c r="I20" s="28"/>
+      <c r="J20" s="28"/>
+      <c r="K20" s="28"/>
+      <c r="L20" s="28"/>
+      <c r="M20" s="28"/>
+      <c r="N20" s="28"/>
+      <c r="O20" s="28"/>
+      <c r="P20" s="28"/>
+      <c r="Q20" s="28"/>
+      <c r="R20" s="28"/>
+      <c r="S20" s="28"/>
+      <c r="T20" s="28"/>
+      <c r="U20" s="28"/>
+      <c r="V20" s="28"/>
+      <c r="W20" s="28"/>
+      <c r="X20" s="28"/>
+      <c r="Y20" s="28"/>
+      <c r="Z20" s="28"/>
+      <c r="AA20" s="28"/>
+      <c r="AB20" s="28"/>
     </row>
     <row r="21" ht="15.0" customHeight="1">
-      <c r="A21" s="28" t="s">
-        <v>468</v>
-      </c>
-      <c r="B21" s="29">
+      <c r="A21" s="29" t="s">
+        <v>471</v>
+      </c>
+      <c r="B21" s="30">
         <v>4329.39</v>
       </c>
-      <c r="C21" s="29">
+      <c r="C21" s="30">
         <v>3949.51</v>
       </c>
-      <c r="D21" s="29">
+      <c r="D21" s="30">
         <v>4448.77</v>
       </c>
-      <c r="E21" s="29">
+      <c r="E21" s="30">
         <v>5249.6</v>
       </c>
-      <c r="F21" s="29">
+      <c r="F21" s="30">
         <v>4536.98</v>
       </c>
-      <c r="G21" s="29">
+      <c r="G21" s="30">
         <v>4303.8</v>
       </c>
-      <c r="H21" s="29">
+      <c r="H21" s="30">
         <v>4262.43</v>
       </c>
-      <c r="I21" s="29">
+      <c r="I21" s="30">
         <v>4198.47</v>
       </c>
-      <c r="J21" s="29">
+      <c r="J21" s="30">
         <v>3234.21</v>
       </c>
-      <c r="K21" s="29">
+      <c r="K21" s="30">
         <v>3228.83</v>
       </c>
-      <c r="L21" s="29">
+      <c r="L21" s="30">
         <v>2543.93</v>
       </c>
-      <c r="M21" s="29">
+      <c r="M21" s="30">
         <v>2408.99</v>
       </c>
-      <c r="N21" s="29">
+      <c r="N21" s="30">
         <v>2232.58</v>
       </c>
-      <c r="O21" s="29">
+      <c r="O21" s="30">
         <v>2188.25</v>
       </c>
-      <c r="P21" s="29">
+      <c r="P21" s="30">
         <v>2160.38</v>
       </c>
-      <c r="Q21" s="29">
+      <c r="Q21" s="30">
         <v>1729.29</v>
       </c>
-      <c r="R21" s="29">
+      <c r="R21" s="30">
         <v>1713.98</v>
       </c>
-      <c r="S21" s="29">
+      <c r="S21" s="30">
         <v>1467.78</v>
       </c>
-      <c r="T21" s="29">
+      <c r="T21" s="30">
         <v>1593.29</v>
       </c>
-      <c r="U21" s="29">
+      <c r="U21" s="30">
         <v>1424.01</v>
       </c>
-      <c r="V21" s="29">
+      <c r="V21" s="30">
         <v>954.08</v>
       </c>
-      <c r="W21" s="29">
+      <c r="W21" s="30">
         <v>932.72</v>
       </c>
-      <c r="X21" s="29">
+      <c r="X21" s="30">
         <v>536.13</v>
       </c>
-      <c r="Y21" s="29">
+      <c r="Y21" s="30">
         <v>517.14</v>
       </c>
-      <c r="Z21" s="29">
+      <c r="Z21" s="30">
         <v>490.69</v>
       </c>
-      <c r="AA21" s="29">
+      <c r="AA21" s="30">
         <v>1790.61</v>
       </c>
-      <c r="AB21" s="29">
+      <c r="AB21" s="30">
         <v>248.74</v>
       </c>
     </row>
     <row r="22" ht="15.0" customHeight="1">
-      <c r="A22" s="28" t="s">
-        <v>469</v>
-      </c>
-      <c r="B22" s="29">
+      <c r="A22" s="29" t="s">
+        <v>472</v>
+      </c>
+      <c r="B22" s="30">
         <v>4948.7</v>
       </c>
-      <c r="C22" s="29">
+      <c r="C22" s="30">
         <v>4859.27</v>
       </c>
-      <c r="D22" s="29">
+      <c r="D22" s="30">
         <v>4716.51</v>
       </c>
-      <c r="E22" s="29">
+      <c r="E22" s="30">
         <v>4508.07</v>
       </c>
-      <c r="F22" s="29">
+      <c r="F22" s="30">
         <v>4364.97</v>
       </c>
-      <c r="G22" s="29">
+      <c r="G22" s="30">
         <v>3909.75</v>
       </c>
-      <c r="H22" s="29">
+      <c r="H22" s="30">
         <v>3627.46</v>
       </c>
-      <c r="I22" s="29">
+      <c r="I22" s="30">
         <v>3326.33</v>
       </c>
-      <c r="J22" s="29">
+      <c r="J22" s="30">
         <v>2845.8</v>
       </c>
-      <c r="K22" s="29">
+      <c r="K22" s="30">
         <v>2867.92</v>
       </c>
-      <c r="L22" s="29">
+      <c r="L22" s="30">
         <v>2593.75</v>
       </c>
-      <c r="M22" s="29">
+      <c r="M22" s="30">
         <v>2271.02</v>
       </c>
-      <c r="N22" s="29">
+      <c r="N22" s="30">
         <v>1834.18</v>
       </c>
-      <c r="O22" s="29">
+      <c r="O22" s="30">
         <v>1749.15</v>
       </c>
-      <c r="P22" s="29">
+      <c r="P22" s="30">
         <v>1621.9</v>
       </c>
-      <c r="Q22" s="29">
+      <c r="Q22" s="30">
         <v>1562.96</v>
       </c>
-      <c r="R22" s="29">
+      <c r="R22" s="30">
         <v>1649.53</v>
       </c>
-      <c r="S22" s="29">
+      <c r="S22" s="30">
         <v>1243.41</v>
       </c>
-      <c r="T22" s="29">
+      <c r="T22" s="30">
         <v>1106.6</v>
       </c>
-      <c r="U22" s="29">
+      <c r="U22" s="30">
         <v>868.58</v>
       </c>
-      <c r="V22" s="29">
+      <c r="V22" s="30">
         <v>700.18</v>
       </c>
-      <c r="W22" s="29">
+      <c r="W22" s="30">
         <v>891.46</v>
       </c>
-      <c r="X22" s="29">
+      <c r="X22" s="30">
         <v>651.16</v>
       </c>
-      <c r="Y22" s="30"/>
-      <c r="Z22" s="30"/>
-      <c r="AA22" s="30"/>
-      <c r="AB22" s="30"/>
+      <c r="Y22" s="31"/>
+      <c r="Z22" s="31"/>
+      <c r="AA22" s="31"/>
+      <c r="AB22" s="31"/>
     </row>
     <row r="23" ht="15.0" customHeight="1">
-      <c r="A23" s="26" t="s">
-        <v>470</v>
-      </c>
-      <c r="B23" s="27"/>
-      <c r="C23" s="27"/>
-      <c r="D23" s="27"/>
-      <c r="E23" s="27"/>
-      <c r="F23" s="27"/>
-      <c r="G23" s="27"/>
-      <c r="H23" s="27"/>
-      <c r="I23" s="27"/>
-      <c r="J23" s="27"/>
-      <c r="K23" s="27"/>
-      <c r="L23" s="27"/>
-      <c r="M23" s="27"/>
-      <c r="N23" s="27"/>
-      <c r="O23" s="27"/>
-      <c r="P23" s="27"/>
-      <c r="Q23" s="27"/>
-      <c r="R23" s="27"/>
-      <c r="S23" s="27"/>
-      <c r="T23" s="27"/>
-      <c r="U23" s="27"/>
-      <c r="V23" s="27"/>
-      <c r="W23" s="27"/>
-      <c r="X23" s="27"/>
-      <c r="Y23" s="27"/>
-      <c r="Z23" s="27"/>
-      <c r="AA23" s="27"/>
-      <c r="AB23" s="27"/>
+      <c r="A23" s="27" t="s">
+        <v>473</v>
+      </c>
+      <c r="B23" s="28"/>
+      <c r="C23" s="28"/>
+      <c r="D23" s="28"/>
+      <c r="E23" s="28"/>
+      <c r="F23" s="28"/>
+      <c r="G23" s="28"/>
+      <c r="H23" s="28"/>
+      <c r="I23" s="28"/>
+      <c r="J23" s="28"/>
+      <c r="K23" s="28"/>
+      <c r="L23" s="28"/>
+      <c r="M23" s="28"/>
+      <c r="N23" s="28"/>
+      <c r="O23" s="28"/>
+      <c r="P23" s="28"/>
+      <c r="Q23" s="28"/>
+      <c r="R23" s="28"/>
+      <c r="S23" s="28"/>
+      <c r="T23" s="28"/>
+      <c r="U23" s="28"/>
+      <c r="V23" s="28"/>
+      <c r="W23" s="28"/>
+      <c r="X23" s="28"/>
+      <c r="Y23" s="28"/>
+      <c r="Z23" s="28"/>
+      <c r="AA23" s="28"/>
+      <c r="AB23" s="28"/>
     </row>
     <row r="24" ht="15.0" customHeight="1">
-      <c r="A24" s="28" t="s">
-        <v>470</v>
-      </c>
-      <c r="B24" s="29">
+      <c r="A24" s="29" t="s">
+        <v>473</v>
+      </c>
+      <c r="B24" s="30">
         <v>1793.12</v>
       </c>
-      <c r="C24" s="29">
+      <c r="C24" s="30">
         <v>2101.56</v>
       </c>
-      <c r="D24" s="29">
+      <c r="D24" s="30">
         <v>2701.19</v>
       </c>
-      <c r="E24" s="29">
+      <c r="E24" s="30">
         <v>3573.39</v>
       </c>
-      <c r="F24" s="29">
+      <c r="F24" s="30">
         <v>2764.94</v>
       </c>
-      <c r="G24" s="29">
+      <c r="G24" s="30">
         <v>2356.02</v>
       </c>
-      <c r="H24" s="29">
+      <c r="H24" s="30">
         <v>2477.92</v>
       </c>
-      <c r="I24" s="29">
+      <c r="I24" s="30">
         <v>3049.58</v>
       </c>
-      <c r="J24" s="29">
+      <c r="J24" s="30">
         <v>2300.72</v>
       </c>
-      <c r="K24" s="29">
+      <c r="K24" s="30">
         <v>2230.24</v>
       </c>
-      <c r="L24" s="29">
+      <c r="L24" s="30">
         <v>1593.11</v>
       </c>
-      <c r="M24" s="29">
+      <c r="M24" s="30">
         <v>1557.0</v>
       </c>
-      <c r="N24" s="29">
+      <c r="N24" s="30">
         <v>1356.35</v>
       </c>
-      <c r="O24" s="29">
+      <c r="O24" s="30">
         <v>1440.67</v>
       </c>
-      <c r="P24" s="29">
+      <c r="P24" s="30">
         <v>1526.98</v>
       </c>
-      <c r="Q24" s="29">
+      <c r="Q24" s="30">
         <v>1142.93</v>
       </c>
-      <c r="R24" s="29">
+      <c r="R24" s="30">
         <v>913.8</v>
       </c>
-      <c r="S24" s="29">
+      <c r="S24" s="30">
         <v>1192.27</v>
       </c>
-      <c r="T24" s="29">
+      <c r="T24" s="30">
         <v>1288.58</v>
       </c>
-      <c r="U24" s="29">
+      <c r="U24" s="30">
         <v>1251.55</v>
       </c>
-      <c r="V24" s="29">
+      <c r="V24" s="30">
         <v>953.27</v>
       </c>
-      <c r="W24" s="29">
+      <c r="W24" s="30">
         <v>825.96</v>
       </c>
-      <c r="X24" s="29">
+      <c r="X24" s="30">
         <v>491.71</v>
       </c>
-      <c r="Y24" s="29">
+      <c r="Y24" s="30">
         <v>389.29</v>
       </c>
-      <c r="Z24" s="29">
+      <c r="Z24" s="30">
         <v>320.45</v>
       </c>
-      <c r="AA24" s="29">
+      <c r="AA24" s="30">
         <v>1669.89</v>
       </c>
-      <c r="AB24" s="29">
+      <c r="AB24" s="30">
         <v>192.63</v>
       </c>
     </row>
     <row r="25" ht="15.0" customHeight="1">
-      <c r="A25" s="28" t="s">
-        <v>471</v>
-      </c>
-      <c r="B25" s="29">
+      <c r="A25" s="29" t="s">
+        <v>474</v>
+      </c>
+      <c r="B25" s="30">
         <v>2868.25</v>
       </c>
-      <c r="C25" s="29">
+      <c r="C25" s="30">
         <v>2921.1</v>
       </c>
-      <c r="D25" s="29">
+      <c r="D25" s="30">
         <v>2868.53</v>
       </c>
-      <c r="E25" s="29">
+      <c r="E25" s="30">
         <v>2843.52</v>
       </c>
-      <c r="F25" s="29">
+      <c r="F25" s="30">
         <v>2758.55</v>
       </c>
-      <c r="G25" s="29">
+      <c r="G25" s="30">
         <v>2528.98</v>
       </c>
-      <c r="H25" s="29">
+      <c r="H25" s="30">
         <v>2421.05</v>
       </c>
-      <c r="I25" s="29">
+      <c r="I25" s="30">
         <v>2280.99</v>
       </c>
-      <c r="J25" s="29">
+      <c r="J25" s="30">
         <v>1876.81</v>
       </c>
-      <c r="K25" s="29">
+      <c r="K25" s="30">
         <v>1855.32</v>
       </c>
-      <c r="L25" s="29">
+      <c r="L25" s="30">
         <v>1681.35</v>
       </c>
-      <c r="M25" s="29">
+      <c r="M25" s="30">
         <v>1486.88</v>
       </c>
-      <c r="N25" s="29">
+      <c r="N25" s="30">
         <v>1172.92</v>
       </c>
-      <c r="O25" s="29">
+      <c r="O25" s="30">
         <v>1183.08</v>
       </c>
-      <c r="P25" s="29">
+      <c r="P25" s="30">
         <v>1144.89</v>
       </c>
-      <c r="Q25" s="29">
+      <c r="Q25" s="30">
         <v>1154.05</v>
       </c>
-      <c r="R25" s="29">
+      <c r="R25" s="30">
         <v>1307.96</v>
       </c>
-      <c r="S25" s="29">
+      <c r="S25" s="30">
         <v>1074.99</v>
       </c>
-      <c r="T25" s="29">
+      <c r="T25" s="30">
         <v>979.0</v>
       </c>
-      <c r="U25" s="29">
+      <c r="U25" s="30">
         <v>778.24</v>
       </c>
-      <c r="V25" s="29">
+      <c r="V25" s="30">
         <v>608.6</v>
       </c>
-      <c r="W25" s="29">
+      <c r="W25" s="30">
         <v>773.21</v>
       </c>
-      <c r="X25" s="29">
+      <c r="X25" s="30">
         <v>558.09</v>
       </c>
-      <c r="Y25" s="30"/>
-      <c r="Z25" s="30"/>
-      <c r="AA25" s="30"/>
-      <c r="AB25" s="30"/>
+      <c r="Y25" s="31"/>
+      <c r="Z25" s="31"/>
+      <c r="AA25" s="31"/>
+      <c r="AB25" s="31"/>
     </row>
     <row r="26" ht="15.0" customHeight="1">
-      <c r="A26" s="26" t="s">
-        <v>472</v>
-      </c>
-      <c r="B26" s="27"/>
-      <c r="C26" s="27"/>
-      <c r="D26" s="27"/>
-      <c r="E26" s="27"/>
-      <c r="F26" s="27"/>
-      <c r="G26" s="27"/>
-      <c r="H26" s="27"/>
-      <c r="I26" s="27"/>
-      <c r="J26" s="27"/>
-      <c r="K26" s="27"/>
-      <c r="L26" s="27"/>
-      <c r="M26" s="27"/>
-      <c r="N26" s="27"/>
-      <c r="O26" s="27"/>
-      <c r="P26" s="27"/>
-      <c r="Q26" s="27"/>
-      <c r="R26" s="27"/>
-      <c r="S26" s="27"/>
-      <c r="T26" s="27"/>
-      <c r="U26" s="27"/>
-      <c r="V26" s="27"/>
-      <c r="W26" s="27"/>
-      <c r="X26" s="27"/>
-      <c r="Y26" s="27"/>
-      <c r="Z26" s="27"/>
-      <c r="AA26" s="27"/>
-      <c r="AB26" s="27"/>
+      <c r="A26" s="27" t="s">
+        <v>475</v>
+      </c>
+      <c r="B26" s="28"/>
+      <c r="C26" s="28"/>
+      <c r="D26" s="28"/>
+      <c r="E26" s="28"/>
+      <c r="F26" s="28"/>
+      <c r="G26" s="28"/>
+      <c r="H26" s="28"/>
+      <c r="I26" s="28"/>
+      <c r="J26" s="28"/>
+      <c r="K26" s="28"/>
+      <c r="L26" s="28"/>
+      <c r="M26" s="28"/>
+      <c r="N26" s="28"/>
+      <c r="O26" s="28"/>
+      <c r="P26" s="28"/>
+      <c r="Q26" s="28"/>
+      <c r="R26" s="28"/>
+      <c r="S26" s="28"/>
+      <c r="T26" s="28"/>
+      <c r="U26" s="28"/>
+      <c r="V26" s="28"/>
+      <c r="W26" s="28"/>
+      <c r="X26" s="28"/>
+      <c r="Y26" s="28"/>
+      <c r="Z26" s="28"/>
+      <c r="AA26" s="28"/>
+      <c r="AB26" s="28"/>
     </row>
     <row r="27" ht="15.0" customHeight="1">
-      <c r="A27" s="28" t="s">
-        <v>473</v>
-      </c>
-      <c r="B27" s="31">
+      <c r="A27" s="29" t="s">
+        <v>476</v>
+      </c>
+      <c r="B27" s="32">
         <v>57.07</v>
       </c>
-      <c r="C27" s="31">
+      <c r="C27" s="32">
         <v>66.89</v>
       </c>
-      <c r="D27" s="31">
+      <c r="D27" s="32">
         <v>85.97</v>
       </c>
-      <c r="E27" s="29">
+      <c r="E27" s="30">
         <v>113.73</v>
       </c>
-      <c r="F27" s="31">
+      <c r="F27" s="32">
         <v>88.0</v>
       </c>
-      <c r="G27" s="31">
+      <c r="G27" s="32">
         <v>74.99</v>
       </c>
-      <c r="H27" s="31">
+      <c r="H27" s="32">
         <v>78.87</v>
       </c>
-      <c r="I27" s="31">
+      <c r="I27" s="32">
         <v>98.45</v>
       </c>
-      <c r="J27" s="31">
+      <c r="J27" s="32">
         <v>74.28</v>
       </c>
-      <c r="K27" s="31">
+      <c r="K27" s="32">
         <v>72.0</v>
       </c>
-      <c r="L27" s="31">
+      <c r="L27" s="32">
         <v>51.43</v>
       </c>
-      <c r="M27" s="31">
+      <c r="M27" s="32">
         <v>50.28</v>
       </c>
-      <c r="N27" s="31">
+      <c r="N27" s="32">
         <v>43.8</v>
       </c>
-      <c r="O27" s="31">
+      <c r="O27" s="32">
         <v>46.53</v>
       </c>
-      <c r="P27" s="31">
+      <c r="P27" s="32">
         <v>53.93</v>
       </c>
-      <c r="Q27" s="31">
+      <c r="Q27" s="32">
         <v>41.03</v>
       </c>
-      <c r="R27" s="31">
+      <c r="R27" s="32">
         <v>32.8</v>
       </c>
-      <c r="S27" s="31">
+      <c r="S27" s="32">
         <v>42.81</v>
       </c>
-      <c r="T27" s="31">
+      <c r="T27" s="32">
         <v>46.89</v>
       </c>
-      <c r="U27" s="31">
+      <c r="U27" s="32">
         <v>46.19</v>
       </c>
-      <c r="V27" s="31">
+      <c r="V27" s="32">
         <v>35.22</v>
       </c>
-      <c r="W27" s="31">
+      <c r="W27" s="32">
         <v>30.52</v>
       </c>
-      <c r="X27" s="31">
+      <c r="X27" s="32">
         <v>18.17</v>
       </c>
-      <c r="Y27" s="31">
+      <c r="Y27" s="32">
         <v>14.02</v>
       </c>
-      <c r="Z27" s="31">
+      <c r="Z27" s="32">
         <v>11.54</v>
       </c>
-      <c r="AA27" s="31">
+      <c r="AA27" s="32">
         <v>10.03</v>
       </c>
-      <c r="AB27" s="31">
+      <c r="AB27" s="32">
         <v>7.32</v>
       </c>
     </row>
     <row r="28" ht="15.0" customHeight="1">
-      <c r="A28" s="28" t="s">
-        <v>474</v>
-      </c>
-      <c r="B28" s="31">
+      <c r="A28" s="29" t="s">
+        <v>477</v>
+      </c>
+      <c r="B28" s="32">
         <v>91.29</v>
       </c>
-      <c r="C28" s="31">
+      <c r="C28" s="32">
         <v>92.97</v>
       </c>
-      <c r="D28" s="31">
+      <c r="D28" s="32">
         <v>91.3</v>
       </c>
-      <c r="E28" s="31">
+      <c r="E28" s="32">
         <v>90.78</v>
       </c>
-      <c r="F28" s="31">
+      <c r="F28" s="32">
         <v>88.34</v>
       </c>
-      <c r="G28" s="31">
+      <c r="G28" s="32">
         <v>81.2</v>
       </c>
-      <c r="H28" s="31">
+      <c r="H28" s="32">
         <v>77.93</v>
       </c>
-      <c r="I28" s="31">
+      <c r="I28" s="32">
         <v>73.64</v>
       </c>
-      <c r="J28" s="31">
+      <c r="J28" s="32">
         <v>60.6</v>
       </c>
-      <c r="K28" s="31">
+      <c r="K28" s="32">
         <v>59.91</v>
       </c>
-      <c r="L28" s="31">
+      <c r="L28" s="32">
         <v>55.37</v>
       </c>
-      <c r="M28" s="31">
+      <c r="M28" s="32">
         <v>49.84</v>
       </c>
-      <c r="N28" s="31">
+      <c r="N28" s="32">
         <v>39.98</v>
       </c>
-      <c r="O28" s="31">
+      <c r="O28" s="32">
         <v>41.26</v>
       </c>
-      <c r="P28" s="31">
+      <c r="P28" s="32">
         <v>41.04</v>
       </c>
-      <c r="Q28" s="31">
+      <c r="Q28" s="32">
         <v>41.82</v>
       </c>
-      <c r="R28" s="31">
+      <c r="R28" s="32">
         <v>47.65</v>
       </c>
-      <c r="S28" s="31">
+      <c r="S28" s="32">
         <v>39.32</v>
       </c>
-      <c r="T28" s="31">
+      <c r="T28" s="32">
         <v>36.02</v>
       </c>
-      <c r="U28" s="31">
+      <c r="U28" s="32">
         <v>28.67</v>
       </c>
-      <c r="V28" s="31">
+      <c r="V28" s="32">
         <v>22.35</v>
       </c>
-      <c r="W28" s="31">
+      <c r="W28" s="32">
         <v>17.69</v>
       </c>
-      <c r="X28" s="31">
+      <c r="X28" s="32">
         <v>11.22</v>
       </c>
-      <c r="Y28" s="30"/>
-      <c r="Z28" s="30"/>
-      <c r="AA28" s="30"/>
-      <c r="AB28" s="30"/>
+      <c r="Y28" s="31"/>
+      <c r="Z28" s="31"/>
+      <c r="AA28" s="31"/>
+      <c r="AB28" s="31"/>
     </row>
     <row r="29" ht="15.0" customHeight="1">
-      <c r="A29" s="26" t="s">
-        <v>475</v>
-      </c>
-      <c r="B29" s="27"/>
-      <c r="C29" s="27"/>
-      <c r="D29" s="27"/>
-      <c r="E29" s="27"/>
-      <c r="F29" s="27"/>
-      <c r="G29" s="27"/>
-      <c r="H29" s="27"/>
-      <c r="I29" s="27"/>
-      <c r="J29" s="27"/>
-      <c r="K29" s="27"/>
-      <c r="L29" s="27"/>
-      <c r="M29" s="27"/>
-      <c r="N29" s="27"/>
-      <c r="O29" s="27"/>
-      <c r="P29" s="27"/>
-      <c r="Q29" s="27"/>
-      <c r="R29" s="27"/>
-      <c r="S29" s="27"/>
-      <c r="T29" s="27"/>
-      <c r="U29" s="27"/>
-      <c r="V29" s="27"/>
-      <c r="W29" s="27"/>
-      <c r="X29" s="27"/>
-      <c r="Y29" s="27"/>
-      <c r="Z29" s="27"/>
-      <c r="AA29" s="27"/>
-      <c r="AB29" s="27"/>
+      <c r="A29" s="27" t="s">
+        <v>478</v>
+      </c>
+      <c r="B29" s="28"/>
+      <c r="C29" s="28"/>
+      <c r="D29" s="28"/>
+      <c r="E29" s="28"/>
+      <c r="F29" s="28"/>
+      <c r="G29" s="28"/>
+      <c r="H29" s="28"/>
+      <c r="I29" s="28"/>
+      <c r="J29" s="28"/>
+      <c r="K29" s="28"/>
+      <c r="L29" s="28"/>
+      <c r="M29" s="28"/>
+      <c r="N29" s="28"/>
+      <c r="O29" s="28"/>
+      <c r="P29" s="28"/>
+      <c r="Q29" s="28"/>
+      <c r="R29" s="28"/>
+      <c r="S29" s="28"/>
+      <c r="T29" s="28"/>
+      <c r="U29" s="28"/>
+      <c r="V29" s="28"/>
+      <c r="W29" s="28"/>
+      <c r="X29" s="28"/>
+      <c r="Y29" s="28"/>
+      <c r="Z29" s="28"/>
+      <c r="AA29" s="28"/>
+      <c r="AB29" s="28"/>
     </row>
     <row r="30" ht="15.0" customHeight="1">
-      <c r="A30" s="28" t="s">
-        <v>476</v>
-      </c>
-      <c r="B30" s="32">
+      <c r="A30" s="29" t="s">
+        <v>479</v>
+      </c>
+      <c r="B30" s="33">
         <v>-10.8</v>
       </c>
-      <c r="C30" s="33">
+      <c r="C30" s="34">
         <v>22.61</v>
       </c>
-      <c r="D30" s="33">
+      <c r="D30" s="34">
         <v>19.02</v>
       </c>
-      <c r="E30" s="33">
+      <c r="E30" s="34">
         <v>8.55</v>
       </c>
-      <c r="F30" s="33">
+      <c r="F30" s="34">
         <v>22.09</v>
       </c>
-      <c r="G30" s="33">
+      <c r="G30" s="34">
         <v>19.91</v>
       </c>
-      <c r="H30" s="32">
+      <c r="H30" s="33">
         <v>-9.29</v>
       </c>
-      <c r="I30" s="33">
+      <c r="I30" s="34">
         <v>4.4</v>
       </c>
-      <c r="J30" s="33">
+      <c r="J30" s="34">
         <v>4.48</v>
       </c>
-      <c r="K30" s="33">
+      <c r="K30" s="34">
         <v>8.51</v>
       </c>
-      <c r="L30" s="33">
+      <c r="L30" s="34">
         <v>2.64</v>
       </c>
-      <c r="M30" s="33">
+      <c r="M30" s="34">
         <v>6.43</v>
       </c>
-      <c r="N30" s="32">
+      <c r="N30" s="33">
         <v>-11.04</v>
       </c>
-      <c r="O30" s="33">
+      <c r="O30" s="34">
         <v>4.14</v>
       </c>
-      <c r="P30" s="33">
+      <c r="P30" s="34">
         <v>3.58</v>
       </c>
-      <c r="Q30" s="33">
+      <c r="Q30" s="34">
         <v>8.35</v>
       </c>
-      <c r="R30" s="33">
+      <c r="R30" s="34">
         <v>11.88</v>
       </c>
-      <c r="S30" s="33">
+      <c r="S30" s="34">
         <v>3.45</v>
       </c>
-      <c r="T30" s="33">
+      <c r="T30" s="34">
         <v>4.51</v>
       </c>
-      <c r="U30" s="33">
+      <c r="U30" s="34">
         <v>12.22</v>
       </c>
-      <c r="V30" s="33">
+      <c r="V30" s="34">
         <v>5.51</v>
       </c>
-      <c r="W30" s="32">
+      <c r="W30" s="33">
         <v>-14.91</v>
       </c>
-      <c r="X30" s="33">
+      <c r="X30" s="34">
         <v>21.0</v>
       </c>
-      <c r="Y30" s="33">
+      <c r="Y30" s="34">
         <v>16.23</v>
       </c>
-      <c r="Z30" s="33">
+      <c r="Z30" s="34">
         <v>8.84</v>
       </c>
-      <c r="AA30" s="32">
+      <c r="AA30" s="33">
         <v>-0.69</v>
       </c>
-      <c r="AB30" s="32">
+      <c r="AB30" s="33">
         <v>-59.84</v>
       </c>
     </row>
     <row r="31" ht="15.0" customHeight="1">
-      <c r="A31" s="28" t="s">
-        <v>477</v>
-      </c>
-      <c r="B31" s="33">
+      <c r="A31" s="29" t="s">
+        <v>480</v>
+      </c>
+      <c r="B31" s="34">
         <v>13.44</v>
       </c>
-      <c r="C31" s="33">
+      <c r="C31" s="34">
         <v>17.46</v>
       </c>
-      <c r="D31" s="33">
+      <c r="D31" s="34">
         <v>11.86</v>
       </c>
-      <c r="E31" s="33">
+      <c r="E31" s="34">
         <v>8.92</v>
       </c>
-      <c r="F31" s="33">
+      <c r="F31" s="34">
         <v>8.16</v>
       </c>
-      <c r="G31" s="33">
+      <c r="G31" s="34">
         <v>5.39</v>
       </c>
-      <c r="H31" s="33">
+      <c r="H31" s="34">
         <v>2.18</v>
       </c>
-      <c r="I31" s="33">
+      <c r="I31" s="34">
         <v>5.3</v>
       </c>
-      <c r="J31" s="33">
+      <c r="J31" s="34">
         <v>2.65</v>
       </c>
-      <c r="K31" s="33">
+      <c r="K31" s="34">
         <v>2.46</v>
       </c>
-      <c r="L31" s="33">
+      <c r="L31" s="34">
         <v>1.23</v>
       </c>
-      <c r="M31" s="33">
+      <c r="M31" s="34">
         <v>2.14</v>
       </c>
-      <c r="N31" s="33">
+      <c r="N31" s="34">
         <v>2.4</v>
       </c>
-      <c r="O31" s="33">
+      <c r="O31" s="34">
         <v>5.62</v>
       </c>
-      <c r="P31" s="33">
+      <c r="P31" s="34">
         <v>5.72</v>
       </c>
-      <c r="Q31" s="33">
+      <c r="Q31" s="34">
         <v>7.79</v>
       </c>
-      <c r="R31" s="33">
+      <c r="R31" s="34">
         <v>7.28</v>
       </c>
-      <c r="S31" s="33">
+      <c r="S31" s="34">
         <v>3.4</v>
       </c>
-      <c r="T31" s="33">
+      <c r="T31" s="34">
         <v>5.4</v>
       </c>
-      <c r="U31" s="33">
+      <c r="U31" s="34">
         <v>6.74</v>
       </c>
-      <c r="V31" s="33">
+      <c r="V31" s="34">
         <v>4.62</v>
       </c>
-      <c r="W31" s="33">
+      <c r="W31" s="34">
         <v>3.64</v>
       </c>
-      <c r="X31" s="33">
+      <c r="X31" s="34">
         <v>5.64</v>
       </c>
-      <c r="Y31" s="33"/>
-      <c r="Z31" s="33"/>
-      <c r="AA31" s="33"/>
-      <c r="AB31" s="33"/>
+      <c r="Y31" s="34"/>
+      <c r="Z31" s="34"/>
+      <c r="AA31" s="34"/>
+      <c r="AB31" s="34"/>
     </row>
     <row r="32" ht="15.0" customHeight="1">
-      <c r="A32" s="26" t="s">
-        <v>478</v>
-      </c>
-      <c r="B32" s="27"/>
-      <c r="C32" s="27"/>
-      <c r="D32" s="27"/>
-      <c r="E32" s="27"/>
-      <c r="F32" s="27"/>
-      <c r="G32" s="27"/>
-      <c r="H32" s="27"/>
-      <c r="I32" s="27"/>
-      <c r="J32" s="27"/>
-      <c r="K32" s="27"/>
-      <c r="L32" s="27"/>
-      <c r="M32" s="27"/>
-      <c r="N32" s="27"/>
-      <c r="O32" s="27"/>
-      <c r="P32" s="27"/>
-      <c r="Q32" s="27"/>
-      <c r="R32" s="27"/>
-      <c r="S32" s="27"/>
-      <c r="T32" s="27"/>
-      <c r="U32" s="27"/>
-      <c r="V32" s="27"/>
-      <c r="W32" s="27"/>
-      <c r="X32" s="27"/>
-      <c r="Y32" s="27"/>
-      <c r="Z32" s="27"/>
-      <c r="AA32" s="27"/>
-      <c r="AB32" s="27"/>
+      <c r="A32" s="27" t="s">
+        <v>481</v>
+      </c>
+      <c r="B32" s="28"/>
+      <c r="C32" s="28"/>
+      <c r="D32" s="28"/>
+      <c r="E32" s="28"/>
+      <c r="F32" s="28"/>
+      <c r="G32" s="28"/>
+      <c r="H32" s="28"/>
+      <c r="I32" s="28"/>
+      <c r="J32" s="28"/>
+      <c r="K32" s="28"/>
+      <c r="L32" s="28"/>
+      <c r="M32" s="28"/>
+      <c r="N32" s="28"/>
+      <c r="O32" s="28"/>
+      <c r="P32" s="28"/>
+      <c r="Q32" s="28"/>
+      <c r="R32" s="28"/>
+      <c r="S32" s="28"/>
+      <c r="T32" s="28"/>
+      <c r="U32" s="28"/>
+      <c r="V32" s="28"/>
+      <c r="W32" s="28"/>
+      <c r="X32" s="28"/>
+      <c r="Y32" s="28"/>
+      <c r="Z32" s="28"/>
+      <c r="AA32" s="28"/>
+      <c r="AB32" s="28"/>
     </row>
     <row r="33" ht="15.0" customHeight="1">
-      <c r="A33" s="28" t="s">
-        <v>479</v>
-      </c>
-      <c r="B33" s="33">
+      <c r="A33" s="29" t="s">
+        <v>482</v>
+      </c>
+      <c r="B33" s="34">
         <v>4.95</v>
       </c>
-      <c r="C33" s="33">
+      <c r="C33" s="34">
         <v>7.69</v>
       </c>
-      <c r="D33" s="33">
+      <c r="D33" s="34">
         <v>5.49</v>
       </c>
-      <c r="E33" s="33">
+      <c r="E33" s="34">
         <v>3.08</v>
       </c>
-      <c r="F33" s="33">
+      <c r="F33" s="34">
         <v>2.62</v>
       </c>
-      <c r="G33" s="33">
+      <c r="G33" s="34">
         <v>5.77</v>
       </c>
-      <c r="H33" s="33">
+      <c r="H33" s="34">
         <v>5.4</v>
       </c>
-      <c r="I33" s="33">
+      <c r="I33" s="34">
         <v>4.2</v>
       </c>
-      <c r="J33" s="33">
+      <c r="J33" s="34">
         <v>5.01</v>
       </c>
-      <c r="K33" s="33">
+      <c r="K33" s="34">
         <v>5.33</v>
       </c>
-      <c r="L33" s="33">
+      <c r="L33" s="34">
         <v>3.69</v>
       </c>
-      <c r="M33" s="33">
+      <c r="M33" s="34">
         <v>0.0</v>
       </c>
-      <c r="N33" s="33">
+      <c r="N33" s="34">
         <v>0.0</v>
       </c>
-      <c r="O33" s="33">
+      <c r="O33" s="34">
         <v>5.61</v>
       </c>
-      <c r="P33" s="33">
+      <c r="P33" s="34">
         <v>4.62</v>
       </c>
-      <c r="Q33" s="33">
+      <c r="Q33" s="34">
         <v>6.47</v>
       </c>
-      <c r="R33" s="33">
+      <c r="R33" s="34">
         <v>9.47</v>
       </c>
-      <c r="S33" s="33">
+      <c r="S33" s="34">
         <v>5.79</v>
       </c>
-      <c r="T33" s="33">
+      <c r="T33" s="34">
         <v>5.35</v>
       </c>
-      <c r="U33" s="33"/>
-      <c r="V33" s="33">
+      <c r="U33" s="34"/>
+      <c r="V33" s="34">
         <v>27.83</v>
       </c>
-      <c r="W33" s="33">
+      <c r="W33" s="34">
         <v>3.65</v>
       </c>
-      <c r="X33" s="33">
+      <c r="X33" s="34">
         <v>7.08</v>
       </c>
-      <c r="Y33" s="33">
+      <c r="Y33" s="34">
         <v>5.38</v>
       </c>
-      <c r="Z33" s="33">
+      <c r="Z33" s="34">
         <v>45.22</v>
       </c>
-      <c r="AA33" s="33">
+      <c r="AA33" s="34">
         <v>2.85</v>
       </c>
-      <c r="AB33" s="33">
+      <c r="AB33" s="34">
         <v>4.33</v>
       </c>
     </row>
     <row r="34" ht="15.0" customHeight="1">
-      <c r="A34" s="28" t="s">
-        <v>480</v>
-      </c>
-      <c r="B34" s="33">
+      <c r="A34" s="29" t="s">
+        <v>483</v>
+      </c>
+      <c r="B34" s="34">
         <v>4.43</v>
       </c>
-      <c r="C34" s="33">
+      <c r="C34" s="34">
         <v>4.62</v>
       </c>
-      <c r="D34" s="33">
+      <c r="D34" s="34">
         <v>4.34</v>
       </c>
-      <c r="E34" s="33">
+      <c r="E34" s="34">
         <v>4.1</v>
       </c>
-      <c r="F34" s="33">
+      <c r="F34" s="34">
         <v>4.55</v>
       </c>
-      <c r="G34" s="33">
+      <c r="G34" s="34">
         <v>5.09</v>
       </c>
-      <c r="H34" s="33">
+      <c r="H34" s="34">
         <v>4.75</v>
       </c>
-      <c r="I34" s="33">
+      <c r="I34" s="34">
         <v>3.85</v>
       </c>
-      <c r="J34" s="33">
+      <c r="J34" s="34">
         <v>3.06</v>
       </c>
-      <c r="K34" s="33">
+      <c r="K34" s="34">
         <v>3.04</v>
       </c>
-      <c r="L34" s="33">
+      <c r="L34" s="34">
         <v>2.83</v>
       </c>
-      <c r="M34" s="33">
+      <c r="M34" s="34">
         <v>3.27</v>
       </c>
-      <c r="N34" s="33">
+      <c r="N34" s="34">
         <v>4.77</v>
       </c>
-      <c r="O34" s="33">
+      <c r="O34" s="34">
         <v>6.04</v>
       </c>
-      <c r="P34" s="33">
+      <c r="P34" s="34">
         <v>5.99</v>
       </c>
-      <c r="Q34" s="33"/>
-      <c r="R34" s="33"/>
-      <c r="S34" s="33"/>
-      <c r="T34" s="33"/>
-      <c r="U34" s="33"/>
-      <c r="V34" s="33">
+      <c r="Q34" s="34"/>
+      <c r="R34" s="34"/>
+      <c r="S34" s="34"/>
+      <c r="T34" s="34"/>
+      <c r="U34" s="34"/>
+      <c r="V34" s="34">
         <v>16.41</v>
       </c>
-      <c r="W34" s="33">
+      <c r="W34" s="34">
         <v>10.17</v>
       </c>
-      <c r="X34" s="33">
+      <c r="X34" s="34">
         <v>12.63</v>
       </c>
-      <c r="Y34" s="33"/>
-      <c r="Z34" s="33"/>
-      <c r="AA34" s="33"/>
-      <c r="AB34" s="33"/>
+      <c r="Y34" s="34"/>
+      <c r="Z34" s="34"/>
+      <c r="AA34" s="34"/>
+      <c r="AB34" s="34"/>
     </row>
     <row r="35" ht="15.0" customHeight="1">
-      <c r="A35" s="28" t="s">
-        <v>481</v>
-      </c>
-      <c r="B35" s="33">
+      <c r="A35" s="29" t="s">
+        <v>484</v>
+      </c>
+      <c r="B35" s="34">
         <v>4.95</v>
       </c>
-      <c r="C35" s="33">
+      <c r="C35" s="34">
         <v>7.69</v>
       </c>
-      <c r="D35" s="33">
+      <c r="D35" s="34">
         <v>5.49</v>
       </c>
-      <c r="E35" s="33">
+      <c r="E35" s="34">
         <v>3.08</v>
       </c>
-      <c r="F35" s="33">
+      <c r="F35" s="34">
         <v>2.62</v>
       </c>
-      <c r="G35" s="33">
+      <c r="G35" s="34">
         <v>5.77</v>
       </c>
-      <c r="H35" s="33">
+      <c r="H35" s="34">
         <v>5.4</v>
       </c>
-      <c r="I35" s="33">
+      <c r="I35" s="34">
         <v>4.2</v>
       </c>
-      <c r="J35" s="33">
+      <c r="J35" s="34">
         <v>5.01</v>
       </c>
-      <c r="K35" s="33">
+      <c r="K35" s="34">
         <v>5.33</v>
       </c>
-      <c r="L35" s="33">
+      <c r="L35" s="34">
         <v>3.69</v>
       </c>
-      <c r="M35" s="33">
+      <c r="M35" s="34">
         <v>0.0</v>
       </c>
-      <c r="N35" s="33">
+      <c r="N35" s="34">
         <v>0.0</v>
       </c>
-      <c r="O35" s="33">
+      <c r="O35" s="34">
         <v>6.98</v>
       </c>
-      <c r="P35" s="33">
+      <c r="P35" s="34">
         <v>5.75</v>
       </c>
-      <c r="Q35" s="33">
+      <c r="Q35" s="34">
         <v>8.05</v>
       </c>
-      <c r="R35" s="33">
+      <c r="R35" s="34">
         <v>11.78</v>
       </c>
-      <c r="S35" s="33">
+      <c r="S35" s="34">
         <v>7.2</v>
       </c>
-      <c r="T35" s="33">
+      <c r="T35" s="34">
         <v>6.65</v>
       </c>
-      <c r="U35" s="33">
+      <c r="U35" s="34">
         <v>6.5</v>
       </c>
-      <c r="V35" s="33">
+      <c r="V35" s="34">
         <v>10.34</v>
       </c>
-      <c r="W35" s="33">
+      <c r="W35" s="34">
         <v>3.65</v>
       </c>
-      <c r="X35" s="33">
+      <c r="X35" s="34">
         <v>7.08</v>
       </c>
-      <c r="Y35" s="33">
+      <c r="Y35" s="34">
         <v>5.38</v>
       </c>
-      <c r="Z35" s="33">
+      <c r="Z35" s="34">
         <v>45.22</v>
       </c>
-      <c r="AA35" s="33">
+      <c r="AA35" s="34">
         <v>2.85</v>
       </c>
-      <c r="AB35" s="33">
+      <c r="AB35" s="34">
         <v>4.33</v>
       </c>
     </row>
     <row r="36" ht="15.0" customHeight="1">
-      <c r="A36" s="28" t="s">
-        <v>482</v>
-      </c>
-      <c r="B36" s="33">
+      <c r="A36" s="29" t="s">
+        <v>485</v>
+      </c>
+      <c r="B36" s="34">
         <v>4.43</v>
       </c>
-      <c r="C36" s="33">
+      <c r="C36" s="34">
         <v>4.62</v>
       </c>
-      <c r="D36" s="33">
+      <c r="D36" s="34">
         <v>4.34</v>
       </c>
-      <c r="E36" s="33">
+      <c r="E36" s="34">
         <v>4.1</v>
       </c>
-      <c r="F36" s="33">
+      <c r="F36" s="34">
         <v>4.55</v>
       </c>
-      <c r="G36" s="33">
+      <c r="G36" s="34">
         <v>5.09</v>
       </c>
-      <c r="H36" s="33">
+      <c r="H36" s="34">
         <v>4.75</v>
       </c>
-      <c r="I36" s="33">
+      <c r="I36" s="34">
         <v>3.85</v>
       </c>
-      <c r="J36" s="33">
+      <c r="J36" s="34">
         <v>3.06</v>
       </c>
-      <c r="K36" s="33">
+      <c r="K36" s="34">
         <v>3.3</v>
       </c>
-      <c r="L36" s="33">
+      <c r="L36" s="34">
         <v>3.36</v>
       </c>
-      <c r="M36" s="33">
+      <c r="M36" s="34">
         <v>4.07</v>
       </c>
-      <c r="N36" s="33">
+      <c r="N36" s="34">
         <v>5.93</v>
       </c>
-      <c r="O36" s="33">
+      <c r="O36" s="34">
         <v>7.51</v>
       </c>
-      <c r="P36" s="33">
+      <c r="P36" s="34">
         <v>7.45</v>
       </c>
-      <c r="Q36" s="33">
+      <c r="Q36" s="34">
         <v>7.69</v>
       </c>
-      <c r="R36" s="33">
+      <c r="R36" s="34">
         <v>8.09</v>
       </c>
-      <c r="S36" s="33">
+      <c r="S36" s="34">
         <v>6.93</v>
       </c>
-      <c r="T36" s="33">
+      <c r="T36" s="34">
         <v>6.88</v>
       </c>
-      <c r="U36" s="33">
+      <c r="U36" s="34">
         <v>6.81</v>
       </c>
-      <c r="V36" s="33">
+      <c r="V36" s="34">
         <v>10.9</v>
       </c>
-      <c r="W36" s="33">
+      <c r="W36" s="34">
         <v>10.17</v>
       </c>
-      <c r="X36" s="33">
+      <c r="X36" s="34">
         <v>12.63</v>
       </c>
-      <c r="Y36" s="33"/>
-      <c r="Z36" s="33"/>
-      <c r="AA36" s="33"/>
-      <c r="AB36" s="33"/>
+      <c r="Y36" s="34"/>
+      <c r="Z36" s="34"/>
+      <c r="AA36" s="34"/>
+      <c r="AB36" s="34"/>
     </row>
     <row r="37" ht="15.0" customHeight="1">
-      <c r="A37" s="26" t="s">
-        <v>483</v>
-      </c>
-      <c r="B37" s="27"/>
-      <c r="C37" s="27"/>
-      <c r="D37" s="27"/>
-      <c r="E37" s="27"/>
-      <c r="F37" s="27"/>
-      <c r="G37" s="27"/>
-      <c r="H37" s="27"/>
-      <c r="I37" s="27"/>
-      <c r="J37" s="27"/>
-      <c r="K37" s="27"/>
-      <c r="L37" s="27"/>
-      <c r="M37" s="27"/>
-      <c r="N37" s="27"/>
-      <c r="O37" s="27"/>
-      <c r="P37" s="27"/>
-      <c r="Q37" s="27"/>
-      <c r="R37" s="27"/>
-      <c r="S37" s="27"/>
-      <c r="T37" s="27"/>
-      <c r="U37" s="27"/>
-      <c r="V37" s="27"/>
-      <c r="W37" s="27"/>
-      <c r="X37" s="27"/>
-      <c r="Y37" s="27"/>
-      <c r="Z37" s="27"/>
-      <c r="AA37" s="27"/>
-      <c r="AB37" s="27"/>
+      <c r="A37" s="27" t="s">
+        <v>486</v>
+      </c>
+      <c r="B37" s="28"/>
+      <c r="C37" s="28"/>
+      <c r="D37" s="28"/>
+      <c r="E37" s="28"/>
+      <c r="F37" s="28"/>
+      <c r="G37" s="28"/>
+      <c r="H37" s="28"/>
+      <c r="I37" s="28"/>
+      <c r="J37" s="28"/>
+      <c r="K37" s="28"/>
+      <c r="L37" s="28"/>
+      <c r="M37" s="28"/>
+      <c r="N37" s="28"/>
+      <c r="O37" s="28"/>
+      <c r="P37" s="28"/>
+      <c r="Q37" s="28"/>
+      <c r="R37" s="28"/>
+      <c r="S37" s="28"/>
+      <c r="T37" s="28"/>
+      <c r="U37" s="28"/>
+      <c r="V37" s="28"/>
+      <c r="W37" s="28"/>
+      <c r="X37" s="28"/>
+      <c r="Y37" s="28"/>
+      <c r="Z37" s="28"/>
+      <c r="AA37" s="28"/>
+      <c r="AB37" s="28"/>
     </row>
     <row r="38" ht="15.0" customHeight="1">
-      <c r="A38" s="28" t="s">
-        <v>484</v>
-      </c>
-      <c r="B38" s="31">
+      <c r="A38" s="29" t="s">
+        <v>487</v>
+      </c>
+      <c r="B38" s="32">
         <v>0.94</v>
       </c>
-      <c r="C38" s="31">
+      <c r="C38" s="32">
         <v>1.34</v>
       </c>
-      <c r="D38" s="31">
+      <c r="D38" s="32">
         <v>1.79</v>
       </c>
-      <c r="E38" s="31">
+      <c r="E38" s="32">
         <v>2.74</v>
       </c>
-      <c r="F38" s="31">
+      <c r="F38" s="32">
         <v>2.31</v>
       </c>
-      <c r="G38" s="31">
+      <c r="G38" s="32">
         <v>1.94</v>
       </c>
-      <c r="H38" s="31">
+      <c r="H38" s="32">
         <v>2.12</v>
       </c>
-      <c r="I38" s="31">
+      <c r="I38" s="32">
         <v>2.73</v>
       </c>
-      <c r="J38" s="31">
+      <c r="J38" s="32">
         <v>2.18</v>
       </c>
-      <c r="K38" s="31">
+      <c r="K38" s="32">
         <v>2.23</v>
       </c>
-      <c r="L38" s="31">
+      <c r="L38" s="32">
         <v>1.66</v>
       </c>
-      <c r="M38" s="31">
+      <c r="M38" s="32">
         <v>1.81</v>
       </c>
-      <c r="N38" s="31">
+      <c r="N38" s="32">
         <v>2.05</v>
       </c>
-      <c r="O38" s="31">
+      <c r="O38" s="32">
         <v>2.01</v>
       </c>
-      <c r="P38" s="31">
+      <c r="P38" s="32">
         <v>2.68</v>
       </c>
-      <c r="Q38" s="31">
+      <c r="Q38" s="32">
         <v>1.9</v>
       </c>
-      <c r="R38" s="31">
+      <c r="R38" s="32">
         <v>1.32</v>
       </c>
-      <c r="S38" s="31">
+      <c r="S38" s="32">
         <v>2.23</v>
       </c>
-      <c r="T38" s="31">
+      <c r="T38" s="32">
         <v>2.52</v>
       </c>
-      <c r="U38" s="31">
+      <c r="U38" s="32">
         <v>2.52</v>
       </c>
-      <c r="V38" s="31">
+      <c r="V38" s="32">
         <v>1.9</v>
       </c>
-      <c r="W38" s="31">
+      <c r="W38" s="32">
         <v>1.67</v>
       </c>
-      <c r="X38" s="31">
+      <c r="X38" s="32">
         <v>1.01</v>
       </c>
-      <c r="Y38" s="31">
+      <c r="Y38" s="32">
         <v>0.83</v>
       </c>
-      <c r="Z38" s="31">
+      <c r="Z38" s="32">
         <v>0.59</v>
       </c>
-      <c r="AA38" s="31">
+      <c r="AA38" s="32">
         <v>0.48</v>
       </c>
-      <c r="AB38" s="31">
+      <c r="AB38" s="32">
         <v>0.3</v>
       </c>
     </row>
     <row r="39" ht="15.0" customHeight="1">
-      <c r="A39" s="28" t="s">
-        <v>485</v>
-      </c>
-      <c r="B39" s="31">
+      <c r="A39" s="29" t="s">
+        <v>488</v>
+      </c>
+      <c r="B39" s="32">
         <v>1.77</v>
       </c>
-      <c r="C39" s="31">
+      <c r="C39" s="32">
         <v>2.0</v>
       </c>
-      <c r="D39" s="31">
+      <c r="D39" s="32">
         <v>2.17</v>
       </c>
-      <c r="E39" s="31">
+      <c r="E39" s="32">
         <v>2.37</v>
       </c>
-      <c r="F39" s="31">
+      <c r="F39" s="32">
         <v>2.25</v>
       </c>
-      <c r="G39" s="31">
+      <c r="G39" s="32">
         <v>2.24</v>
       </c>
-      <c r="H39" s="31">
+      <c r="H39" s="32">
         <v>2.19</v>
       </c>
-      <c r="I39" s="31">
+      <c r="I39" s="32">
         <v>2.13</v>
       </c>
-      <c r="J39" s="31">
+      <c r="J39" s="32">
         <v>1.99</v>
       </c>
-      <c r="K39" s="31">
+      <c r="K39" s="32">
         <v>1.95</v>
       </c>
-      <c r="L39" s="31">
+      <c r="L39" s="32">
         <v>2.01</v>
       </c>
-      <c r="M39" s="31">
+      <c r="M39" s="32">
         <v>2.07</v>
       </c>
-      <c r="N39" s="31">
+      <c r="N39" s="32">
         <v>2.0</v>
       </c>
-      <c r="O39" s="31">
+      <c r="O39" s="32">
         <v>2.03</v>
       </c>
-      <c r="P39" s="31">
+      <c r="P39" s="32">
         <v>2.12</v>
       </c>
-      <c r="Q39" s="31">
+      <c r="Q39" s="32">
         <v>2.08</v>
       </c>
-      <c r="R39" s="31">
+      <c r="R39" s="32">
         <v>2.08</v>
       </c>
-      <c r="S39" s="31">
+      <c r="S39" s="32">
         <v>2.17</v>
       </c>
-      <c r="T39" s="31">
+      <c r="T39" s="32">
         <v>1.91</v>
       </c>
-      <c r="U39" s="31">
+      <c r="U39" s="32">
         <v>1.58</v>
       </c>
-      <c r="V39" s="31">
+      <c r="V39" s="32">
         <v>1.19</v>
       </c>
-      <c r="W39" s="31">
+      <c r="W39" s="32">
         <v>0.9</v>
       </c>
-      <c r="X39" s="31">
+      <c r="X39" s="32">
         <v>0.63</v>
       </c>
-      <c r="Y39" s="30"/>
-      <c r="Z39" s="30"/>
-      <c r="AA39" s="30"/>
-      <c r="AB39" s="30"/>
+      <c r="Y39" s="31"/>
+      <c r="Z39" s="31"/>
+      <c r="AA39" s="31"/>
+      <c r="AB39" s="31"/>
     </row>
     <row r="40" ht="15.0" customHeight="1">
-      <c r="A40" s="26" t="s">
-        <v>486</v>
-      </c>
-      <c r="B40" s="27"/>
-      <c r="C40" s="27"/>
-      <c r="D40" s="27"/>
-      <c r="E40" s="27"/>
-      <c r="F40" s="27"/>
-      <c r="G40" s="27"/>
-      <c r="H40" s="27"/>
-      <c r="I40" s="27"/>
-      <c r="J40" s="27"/>
-      <c r="K40" s="27"/>
-      <c r="L40" s="27"/>
-      <c r="M40" s="27"/>
-      <c r="N40" s="27"/>
-      <c r="O40" s="27"/>
-      <c r="P40" s="27"/>
-      <c r="Q40" s="27"/>
-      <c r="R40" s="27"/>
-      <c r="S40" s="27"/>
-      <c r="T40" s="27"/>
-      <c r="U40" s="27"/>
-      <c r="V40" s="27"/>
-      <c r="W40" s="27"/>
-      <c r="X40" s="27"/>
-      <c r="Y40" s="27"/>
-      <c r="Z40" s="27"/>
-      <c r="AA40" s="27"/>
-      <c r="AB40" s="27"/>
+      <c r="A40" s="27" t="s">
+        <v>489</v>
+      </c>
+      <c r="B40" s="28"/>
+      <c r="C40" s="28"/>
+      <c r="D40" s="28"/>
+      <c r="E40" s="28"/>
+      <c r="F40" s="28"/>
+      <c r="G40" s="28"/>
+      <c r="H40" s="28"/>
+      <c r="I40" s="28"/>
+      <c r="J40" s="28"/>
+      <c r="K40" s="28"/>
+      <c r="L40" s="28"/>
+      <c r="M40" s="28"/>
+      <c r="N40" s="28"/>
+      <c r="O40" s="28"/>
+      <c r="P40" s="28"/>
+      <c r="Q40" s="28"/>
+      <c r="R40" s="28"/>
+      <c r="S40" s="28"/>
+      <c r="T40" s="28"/>
+      <c r="U40" s="28"/>
+      <c r="V40" s="28"/>
+      <c r="W40" s="28"/>
+      <c r="X40" s="28"/>
+      <c r="Y40" s="28"/>
+      <c r="Z40" s="28"/>
+      <c r="AA40" s="28"/>
+      <c r="AB40" s="28"/>
     </row>
     <row r="41" ht="15.0" customHeight="1">
-      <c r="A41" s="28" t="s">
-        <v>487</v>
-      </c>
-      <c r="B41" s="31">
+      <c r="A41" s="29" t="s">
+        <v>490</v>
+      </c>
+      <c r="B41" s="32">
         <v>2.75</v>
       </c>
-      <c r="C41" s="31">
+      <c r="C41" s="32">
         <v>2.12</v>
       </c>
-      <c r="D41" s="31">
+      <c r="D41" s="32">
         <v>2.65</v>
       </c>
-      <c r="E41" s="31">
+      <c r="E41" s="32">
         <v>4.25</v>
       </c>
-      <c r="F41" s="31">
+      <c r="F41" s="32">
         <v>4.51</v>
       </c>
-      <c r="G41" s="31">
+      <c r="G41" s="32">
         <v>3.35</v>
       </c>
-      <c r="H41" s="31">
+      <c r="H41" s="32">
         <v>3.83</v>
       </c>
-      <c r="I41" s="31">
+      <c r="I41" s="32">
         <v>4.92</v>
       </c>
-      <c r="J41" s="31">
+      <c r="J41" s="32">
         <v>4.01</v>
       </c>
-      <c r="K41" s="31">
+      <c r="K41" s="32">
         <v>4.68</v>
       </c>
-      <c r="L41" s="31">
+      <c r="L41" s="32">
         <v>3.65</v>
       </c>
-      <c r="M41" s="31">
+      <c r="M41" s="32">
         <v>4.21</v>
       </c>
-      <c r="N41" s="31">
+      <c r="N41" s="32">
         <v>6.25</v>
       </c>
-      <c r="O41" s="31">
+      <c r="O41" s="32">
         <v>12.72</v>
       </c>
-      <c r="P41" s="30"/>
-      <c r="Q41" s="30"/>
-      <c r="R41" s="29">
+      <c r="P41" s="31"/>
+      <c r="Q41" s="31"/>
+      <c r="R41" s="30">
         <v>2728.74</v>
       </c>
-      <c r="S41" s="31">
+      <c r="S41" s="32">
         <v>2.94</v>
       </c>
-      <c r="T41" s="31">
+      <c r="T41" s="32">
         <v>3.03</v>
       </c>
-      <c r="U41" s="31">
+      <c r="U41" s="32">
         <v>2.54</v>
       </c>
-      <c r="V41" s="31">
+      <c r="V41" s="32">
         <v>2.01</v>
       </c>
-      <c r="W41" s="31">
+      <c r="W41" s="32">
         <v>1.78</v>
       </c>
-      <c r="X41" s="31">
+      <c r="X41" s="32">
         <v>1.09</v>
       </c>
-      <c r="Y41" s="31">
+      <c r="Y41" s="32">
         <v>0.85</v>
       </c>
-      <c r="Z41" s="31">
+      <c r="Z41" s="32">
         <v>0.61</v>
       </c>
-      <c r="AA41" s="31">
+      <c r="AA41" s="32">
         <v>0.49</v>
       </c>
-      <c r="AB41" s="31">
+      <c r="AB41" s="32">
         <v>0.3</v>
       </c>
     </row>
     <row r="42" ht="15.0" customHeight="1">
-      <c r="A42" s="28" t="s">
-        <v>488</v>
-      </c>
-      <c r="B42" s="31">
+      <c r="A42" s="29" t="s">
+        <v>491</v>
+      </c>
+      <c r="B42" s="32">
         <v>3.18</v>
       </c>
-      <c r="C42" s="31">
+      <c r="C42" s="32">
         <v>3.27</v>
       </c>
-      <c r="D42" s="31">
+      <c r="D42" s="32">
         <v>3.63</v>
       </c>
-      <c r="E42" s="31">
+      <c r="E42" s="32">
         <v>4.15</v>
       </c>
-      <c r="F42" s="31">
+      <c r="F42" s="32">
         <v>4.09</v>
       </c>
-      <c r="G42" s="31">
+      <c r="G42" s="32">
         <v>4.11</v>
       </c>
-      <c r="H42" s="31">
+      <c r="H42" s="32">
         <v>4.22</v>
       </c>
-      <c r="I42" s="31">
+      <c r="I42" s="32">
         <v>4.31</v>
       </c>
-      <c r="J42" s="31">
+      <c r="J42" s="32">
         <v>4.4</v>
       </c>
-      <c r="K42" s="31">
+      <c r="K42" s="32">
         <v>5.18</v>
       </c>
-      <c r="L42" s="31">
+      <c r="L42" s="32">
         <v>7.16</v>
       </c>
-      <c r="M42" s="31">
+      <c r="M42" s="32">
         <v>12.12</v>
       </c>
-      <c r="N42" s="31">
+      <c r="N42" s="32">
         <v>26.32</v>
       </c>
-      <c r="O42" s="31">
+      <c r="O42" s="32">
         <v>13.94</v>
       </c>
-      <c r="P42" s="31">
+      <c r="P42" s="32">
         <v>7.93</v>
       </c>
-      <c r="Q42" s="31">
+      <c r="Q42" s="32">
         <v>4.39</v>
       </c>
-      <c r="R42" s="31">
+      <c r="R42" s="32">
         <v>3.02</v>
       </c>
-      <c r="S42" s="31">
+      <c r="S42" s="32">
         <v>2.44</v>
       </c>
-      <c r="T42" s="31">
+      <c r="T42" s="32">
         <v>2.06</v>
       </c>
-      <c r="U42" s="31">
+      <c r="U42" s="32">
         <v>1.66</v>
       </c>
-      <c r="V42" s="31">
+      <c r="V42" s="32">
         <v>1.25</v>
       </c>
-      <c r="W42" s="31">
+      <c r="W42" s="32">
         <v>0.94</v>
       </c>
-      <c r="X42" s="31">
+      <c r="X42" s="32">
         <v>0.65</v>
       </c>
-      <c r="Y42" s="30"/>
-      <c r="Z42" s="30"/>
-      <c r="AA42" s="30"/>
-      <c r="AB42" s="30"/>
+      <c r="Y42" s="31"/>
+      <c r="Z42" s="31"/>
+      <c r="AA42" s="31"/>
+      <c r="AB42" s="31"/>
     </row>
     <row r="43" ht="15.0" customHeight="1">
-      <c r="A43" s="26" t="s">
-        <v>489</v>
-      </c>
-      <c r="B43" s="27"/>
-      <c r="C43" s="27"/>
-      <c r="D43" s="27"/>
-      <c r="E43" s="27"/>
-      <c r="F43" s="27"/>
-      <c r="G43" s="27"/>
-      <c r="H43" s="27"/>
-      <c r="I43" s="27"/>
-      <c r="J43" s="27"/>
-      <c r="K43" s="27"/>
-      <c r="L43" s="27"/>
-      <c r="M43" s="27"/>
-      <c r="N43" s="27"/>
-      <c r="O43" s="27"/>
-      <c r="P43" s="27"/>
-      <c r="Q43" s="27"/>
-      <c r="R43" s="27"/>
-      <c r="S43" s="27"/>
-      <c r="T43" s="27"/>
-      <c r="U43" s="27"/>
-      <c r="V43" s="27"/>
-      <c r="W43" s="27"/>
-      <c r="X43" s="27"/>
-      <c r="Y43" s="27"/>
-      <c r="Z43" s="27"/>
-      <c r="AA43" s="27"/>
-      <c r="AB43" s="27"/>
+      <c r="A43" s="27" t="s">
+        <v>492</v>
+      </c>
+      <c r="B43" s="28"/>
+      <c r="C43" s="28"/>
+      <c r="D43" s="28"/>
+      <c r="E43" s="28"/>
+      <c r="F43" s="28"/>
+      <c r="G43" s="28"/>
+      <c r="H43" s="28"/>
+      <c r="I43" s="28"/>
+      <c r="J43" s="28"/>
+      <c r="K43" s="28"/>
+      <c r="L43" s="28"/>
+      <c r="M43" s="28"/>
+      <c r="N43" s="28"/>
+      <c r="O43" s="28"/>
+      <c r="P43" s="28"/>
+      <c r="Q43" s="28"/>
+      <c r="R43" s="28"/>
+      <c r="S43" s="28"/>
+      <c r="T43" s="28"/>
+      <c r="U43" s="28"/>
+      <c r="V43" s="28"/>
+      <c r="W43" s="28"/>
+      <c r="X43" s="28"/>
+      <c r="Y43" s="28"/>
+      <c r="Z43" s="28"/>
+      <c r="AA43" s="28"/>
+      <c r="AB43" s="28"/>
     </row>
     <row r="44" ht="15.0" customHeight="1">
-      <c r="A44" s="28" t="s">
-        <v>490</v>
-      </c>
-      <c r="B44" s="31">
+      <c r="A44" s="29" t="s">
+        <v>493</v>
+      </c>
+      <c r="B44" s="32">
         <v>0.26</v>
       </c>
-      <c r="C44" s="31">
+      <c r="C44" s="32">
         <v>0.35</v>
       </c>
-      <c r="D44" s="31">
+      <c r="D44" s="32">
         <v>0.5</v>
       </c>
-      <c r="E44" s="31">
+      <c r="E44" s="32">
         <v>0.62</v>
       </c>
-      <c r="F44" s="31">
+      <c r="F44" s="32">
         <v>0.55</v>
       </c>
-      <c r="G44" s="31">
+      <c r="G44" s="32">
         <v>0.4</v>
       </c>
-      <c r="H44" s="31">
+      <c r="H44" s="32">
         <v>0.45</v>
       </c>
-      <c r="I44" s="31">
+      <c r="I44" s="32">
         <v>0.61</v>
       </c>
-      <c r="J44" s="31">
+      <c r="J44" s="32">
         <v>0.55</v>
       </c>
-      <c r="K44" s="31">
+      <c r="K44" s="32">
         <v>0.51</v>
       </c>
-      <c r="L44" s="31">
+      <c r="L44" s="32">
         <v>0.36</v>
       </c>
-      <c r="M44" s="31">
+      <c r="M44" s="32">
         <v>0.4</v>
       </c>
-      <c r="N44" s="31">
+      <c r="N44" s="32">
         <v>0.4</v>
       </c>
-      <c r="O44" s="31">
+      <c r="O44" s="32">
         <v>0.39</v>
       </c>
-      <c r="P44" s="31">
+      <c r="P44" s="32">
         <v>0.51</v>
       </c>
-      <c r="Q44" s="31">
+      <c r="Q44" s="32">
         <v>0.42</v>
       </c>
-      <c r="R44" s="31">
+      <c r="R44" s="32">
         <v>0.26</v>
       </c>
-      <c r="S44" s="31">
+      <c r="S44" s="32">
         <v>0.73</v>
       </c>
-      <c r="T44" s="31">
+      <c r="T44" s="32">
         <v>0.72</v>
       </c>
-      <c r="U44" s="31">
+      <c r="U44" s="32">
         <v>0.81</v>
       </c>
-      <c r="V44" s="31">
+      <c r="V44" s="32">
         <v>0.63</v>
       </c>
-      <c r="W44" s="31">
+      <c r="W44" s="32">
         <v>0.64</v>
       </c>
-      <c r="X44" s="31">
+      <c r="X44" s="32">
         <v>0.46</v>
       </c>
-      <c r="Y44" s="31">
+      <c r="Y44" s="32">
         <v>0.38</v>
       </c>
-      <c r="Z44" s="31">
+      <c r="Z44" s="32">
         <v>0.34</v>
       </c>
-      <c r="AA44" s="31">
+      <c r="AA44" s="32">
         <v>0.39</v>
       </c>
-      <c r="AB44" s="31">
+      <c r="AB44" s="32">
         <v>0.27</v>
       </c>
     </row>
     <row r="45" ht="15.0" customHeight="1">
-      <c r="A45" s="28" t="s">
-        <v>491</v>
-      </c>
-      <c r="B45" s="31">
+      <c r="A45" s="29" t="s">
+        <v>494</v>
+      </c>
+      <c r="B45" s="32">
         <v>0.45</v>
       </c>
-      <c r="C45" s="31">
+      <c r="C45" s="32">
         <v>0.48</v>
       </c>
-      <c r="D45" s="31">
+      <c r="D45" s="32">
         <v>0.5</v>
       </c>
-      <c r="E45" s="31">
+      <c r="E45" s="32">
         <v>0.52</v>
       </c>
-      <c r="F45" s="31">
+      <c r="F45" s="32">
         <v>0.51</v>
       </c>
-      <c r="G45" s="31">
+      <c r="G45" s="32">
         <v>0.5</v>
       </c>
-      <c r="H45" s="31">
+      <c r="H45" s="32">
         <v>0.49</v>
       </c>
-      <c r="I45" s="31">
+      <c r="I45" s="32">
         <v>0.49</v>
       </c>
-      <c r="J45" s="31">
+      <c r="J45" s="32">
         <v>0.44</v>
       </c>
-      <c r="K45" s="31">
+      <c r="K45" s="32">
         <v>0.41</v>
       </c>
-      <c r="L45" s="31">
+      <c r="L45" s="32">
         <v>0.41</v>
       </c>
-      <c r="M45" s="31">
+      <c r="M45" s="32">
         <v>0.42</v>
       </c>
-      <c r="N45" s="31">
+      <c r="N45" s="32">
         <v>0.4</v>
       </c>
-      <c r="O45" s="31">
+      <c r="O45" s="32">
         <v>0.44</v>
       </c>
-      <c r="P45" s="31">
+      <c r="P45" s="32">
         <v>0.49</v>
       </c>
-      <c r="Q45" s="31">
+      <c r="Q45" s="32">
         <v>0.54</v>
       </c>
-      <c r="R45" s="31">
+      <c r="R45" s="32">
         <v>0.58</v>
       </c>
-      <c r="S45" s="31">
+      <c r="S45" s="32">
         <v>0.71</v>
       </c>
-      <c r="T45" s="31">
+      <c r="T45" s="32">
         <v>0.66</v>
       </c>
-      <c r="U45" s="31">
+      <c r="U45" s="32">
         <v>0.6</v>
       </c>
-      <c r="V45" s="31">
+      <c r="V45" s="32">
         <v>0.51</v>
       </c>
-      <c r="W45" s="31">
+      <c r="W45" s="32">
         <v>0.46</v>
       </c>
-      <c r="X45" s="31">
+      <c r="X45" s="32">
         <v>0.38</v>
       </c>
-      <c r="Y45" s="30"/>
-      <c r="Z45" s="30"/>
-      <c r="AA45" s="30"/>
-      <c r="AB45" s="30"/>
+      <c r="Y45" s="31"/>
+      <c r="Z45" s="31"/>
+      <c r="AA45" s="31"/>
+      <c r="AB45" s="31"/>
     </row>
     <row r="46" ht="15.0" customHeight="1">
-      <c r="A46" s="26" t="s">
-        <v>492</v>
-      </c>
-      <c r="B46" s="27"/>
-      <c r="C46" s="27"/>
-      <c r="D46" s="27"/>
-      <c r="E46" s="27"/>
-      <c r="F46" s="27"/>
-      <c r="G46" s="27"/>
-      <c r="H46" s="27"/>
-      <c r="I46" s="27"/>
-      <c r="J46" s="27"/>
-      <c r="K46" s="27"/>
-      <c r="L46" s="27"/>
-      <c r="M46" s="27"/>
-      <c r="N46" s="27"/>
-      <c r="O46" s="27"/>
-      <c r="P46" s="27"/>
-      <c r="Q46" s="27"/>
-      <c r="R46" s="27"/>
-      <c r="S46" s="27"/>
-      <c r="T46" s="27"/>
-      <c r="U46" s="27"/>
-      <c r="V46" s="27"/>
-      <c r="W46" s="27"/>
-      <c r="X46" s="27"/>
-      <c r="Y46" s="27"/>
-      <c r="Z46" s="27"/>
-      <c r="AA46" s="27"/>
-      <c r="AB46" s="27"/>
+      <c r="A46" s="27" t="s">
+        <v>495</v>
+      </c>
+      <c r="B46" s="28"/>
+      <c r="C46" s="28"/>
+      <c r="D46" s="28"/>
+      <c r="E46" s="28"/>
+      <c r="F46" s="28"/>
+      <c r="G46" s="28"/>
+      <c r="H46" s="28"/>
+      <c r="I46" s="28"/>
+      <c r="J46" s="28"/>
+      <c r="K46" s="28"/>
+      <c r="L46" s="28"/>
+      <c r="M46" s="28"/>
+      <c r="N46" s="28"/>
+      <c r="O46" s="28"/>
+      <c r="P46" s="28"/>
+      <c r="Q46" s="28"/>
+      <c r="R46" s="28"/>
+      <c r="S46" s="28"/>
+      <c r="T46" s="28"/>
+      <c r="U46" s="28"/>
+      <c r="V46" s="28"/>
+      <c r="W46" s="28"/>
+      <c r="X46" s="28"/>
+      <c r="Y46" s="28"/>
+      <c r="Z46" s="28"/>
+      <c r="AA46" s="28"/>
+      <c r="AB46" s="28"/>
     </row>
     <row r="47" ht="15.0" customHeight="1">
-      <c r="A47" s="28" t="s">
-        <v>493</v>
-      </c>
-      <c r="B47" s="30"/>
-      <c r="C47" s="31">
+      <c r="A47" s="29" t="s">
+        <v>496</v>
+      </c>
+      <c r="B47" s="31"/>
+      <c r="C47" s="32">
         <v>4.42</v>
       </c>
-      <c r="D47" s="31">
+      <c r="D47" s="32">
         <v>5.26</v>
       </c>
-      <c r="E47" s="31">
+      <c r="E47" s="32">
         <v>11.7</v>
       </c>
-      <c r="F47" s="31">
+      <c r="F47" s="32">
         <v>4.53</v>
       </c>
-      <c r="G47" s="31">
+      <c r="G47" s="32">
         <v>5.02</v>
       </c>
-      <c r="H47" s="30"/>
-      <c r="I47" s="31">
+      <c r="H47" s="31"/>
+      <c r="I47" s="32">
         <v>22.71</v>
       </c>
-      <c r="J47" s="31">
+      <c r="J47" s="32">
         <v>22.3</v>
       </c>
-      <c r="K47" s="31">
+      <c r="K47" s="32">
         <v>11.75</v>
       </c>
-      <c r="L47" s="31">
+      <c r="L47" s="32">
         <v>37.93</v>
       </c>
-      <c r="M47" s="31">
+      <c r="M47" s="32">
         <v>15.56</v>
       </c>
-      <c r="N47" s="30"/>
-      <c r="O47" s="31">
+      <c r="N47" s="31"/>
+      <c r="O47" s="32">
         <v>24.13</v>
       </c>
-      <c r="P47" s="31">
+      <c r="P47" s="32">
         <v>27.9</v>
       </c>
-      <c r="Q47" s="31">
+      <c r="Q47" s="32">
         <v>11.97</v>
       </c>
-      <c r="R47" s="31">
+      <c r="R47" s="32">
         <v>8.42</v>
       </c>
-      <c r="S47" s="31">
+      <c r="S47" s="32">
         <v>28.99</v>
       </c>
-      <c r="T47" s="31">
+      <c r="T47" s="32">
         <v>22.18</v>
       </c>
-      <c r="U47" s="31">
+      <c r="U47" s="32">
         <v>8.18</v>
       </c>
-      <c r="V47" s="31">
+      <c r="V47" s="32">
         <v>18.15</v>
       </c>
-      <c r="W47" s="30"/>
-      <c r="X47" s="31">
+      <c r="W47" s="31"/>
+      <c r="X47" s="32">
         <v>4.76</v>
       </c>
-      <c r="Y47" s="31">
+      <c r="Y47" s="32">
         <v>6.16</v>
       </c>
-      <c r="Z47" s="31">
+      <c r="Z47" s="32">
         <v>11.32</v>
       </c>
-      <c r="AA47" s="30"/>
-      <c r="AB47" s="30"/>
+      <c r="AA47" s="31"/>
+      <c r="AB47" s="31"/>
     </row>
     <row r="48" ht="15.0" customHeight="1">
-      <c r="A48" s="28" t="s">
-        <v>494</v>
-      </c>
-      <c r="B48" s="31">
+      <c r="A48" s="29" t="s">
+        <v>497</v>
+      </c>
+      <c r="B48" s="32">
         <v>7.44</v>
       </c>
-      <c r="C48" s="31">
+      <c r="C48" s="32">
         <v>5.73</v>
       </c>
-      <c r="D48" s="31">
+      <c r="D48" s="32">
         <v>8.43</v>
       </c>
-      <c r="E48" s="31">
+      <c r="E48" s="32">
         <v>11.21</v>
       </c>
-      <c r="F48" s="31">
+      <c r="F48" s="32">
         <v>12.26</v>
       </c>
-      <c r="G48" s="31">
+      <c r="G48" s="32">
         <v>18.56</v>
       </c>
-      <c r="H48" s="31">
+      <c r="H48" s="32">
         <v>45.95</v>
       </c>
-      <c r="I48" s="31">
+      <c r="I48" s="32">
         <v>18.86</v>
       </c>
-      <c r="J48" s="31">
+      <c r="J48" s="32">
         <v>37.76</v>
       </c>
-      <c r="K48" s="31">
+      <c r="K48" s="32">
         <v>40.72</v>
       </c>
-      <c r="L48" s="31">
+      <c r="L48" s="32">
         <v>81.38</v>
       </c>
-      <c r="M48" s="31">
+      <c r="M48" s="32">
         <v>46.73</v>
       </c>
-      <c r="N48" s="31">
+      <c r="N48" s="32">
         <v>41.69</v>
       </c>
-      <c r="O48" s="31">
+      <c r="O48" s="32">
         <v>17.8</v>
       </c>
-      <c r="P48" s="31">
+      <c r="P48" s="32">
         <v>17.5</v>
       </c>
-      <c r="Q48" s="31">
+      <c r="Q48" s="32">
         <v>12.83</v>
       </c>
-      <c r="R48" s="31">
+      <c r="R48" s="32">
         <v>13.73</v>
       </c>
-      <c r="S48" s="31">
+      <c r="S48" s="32">
         <v>29.4</v>
       </c>
-      <c r="T48" s="31">
+      <c r="T48" s="32">
         <v>18.53</v>
       </c>
-      <c r="U48" s="31">
+      <c r="U48" s="32">
         <v>14.83</v>
       </c>
-      <c r="V48" s="31">
+      <c r="V48" s="32">
         <v>21.63</v>
       </c>
-      <c r="W48" s="31">
+      <c r="W48" s="32">
         <v>27.5</v>
       </c>
-      <c r="X48" s="31">
+      <c r="X48" s="32">
         <v>17.72</v>
       </c>
-      <c r="Y48" s="30"/>
-      <c r="Z48" s="30"/>
-      <c r="AA48" s="30"/>
-      <c r="AB48" s="30"/>
+      <c r="Y48" s="31"/>
+      <c r="Z48" s="31"/>
+      <c r="AA48" s="31"/>
+      <c r="AB48" s="31"/>
     </row>
     <row r="49" ht="15.0" customHeight="1">
-      <c r="A49" s="26" t="s">
-        <v>495</v>
-      </c>
-      <c r="B49" s="27"/>
-      <c r="C49" s="27"/>
-      <c r="D49" s="27"/>
-      <c r="E49" s="27"/>
-      <c r="F49" s="27"/>
-      <c r="G49" s="27"/>
-      <c r="H49" s="27"/>
-      <c r="I49" s="27"/>
-      <c r="J49" s="27"/>
-      <c r="K49" s="27"/>
-      <c r="L49" s="27"/>
-      <c r="M49" s="27"/>
-      <c r="N49" s="27"/>
-      <c r="O49" s="27"/>
-      <c r="P49" s="27"/>
-      <c r="Q49" s="27"/>
-      <c r="R49" s="27"/>
-      <c r="S49" s="27"/>
-      <c r="T49" s="27"/>
-      <c r="U49" s="27"/>
-      <c r="V49" s="27"/>
-      <c r="W49" s="27"/>
-      <c r="X49" s="27"/>
-      <c r="Y49" s="27"/>
-      <c r="Z49" s="27"/>
-      <c r="AA49" s="27"/>
-      <c r="AB49" s="27"/>
+      <c r="A49" s="27" t="s">
+        <v>498</v>
+      </c>
+      <c r="B49" s="28"/>
+      <c r="C49" s="28"/>
+      <c r="D49" s="28"/>
+      <c r="E49" s="28"/>
+      <c r="F49" s="28"/>
+      <c r="G49" s="28"/>
+      <c r="H49" s="28"/>
+      <c r="I49" s="28"/>
+      <c r="J49" s="28"/>
+      <c r="K49" s="28"/>
+      <c r="L49" s="28"/>
+      <c r="M49" s="28"/>
+      <c r="N49" s="28"/>
+      <c r="O49" s="28"/>
+      <c r="P49" s="28"/>
+      <c r="Q49" s="28"/>
+      <c r="R49" s="28"/>
+      <c r="S49" s="28"/>
+      <c r="T49" s="28"/>
+      <c r="U49" s="28"/>
+      <c r="V49" s="28"/>
+      <c r="W49" s="28"/>
+      <c r="X49" s="28"/>
+      <c r="Y49" s="28"/>
+      <c r="Z49" s="28"/>
+      <c r="AA49" s="28"/>
+      <c r="AB49" s="28"/>
     </row>
     <row r="50" ht="15.0" customHeight="1">
-      <c r="A50" s="28" t="s">
-        <v>496</v>
-      </c>
-      <c r="B50" s="31">
+      <c r="A50" s="29" t="s">
+        <v>499</v>
+      </c>
+      <c r="B50" s="32">
         <v>3.89</v>
       </c>
-      <c r="C50" s="31">
+      <c r="C50" s="32">
         <v>3.77</v>
       </c>
-      <c r="D50" s="31">
+      <c r="D50" s="32">
         <v>4.35</v>
       </c>
-      <c r="E50" s="31">
+      <c r="E50" s="32">
         <v>6.11</v>
       </c>
-      <c r="F50" s="31">
+      <c r="F50" s="32">
         <v>6.63</v>
       </c>
-      <c r="G50" s="31">
+      <c r="G50" s="32">
         <v>5.3</v>
       </c>
-      <c r="H50" s="31">
+      <c r="H50" s="32">
         <v>9.48</v>
       </c>
-      <c r="I50" s="31">
+      <c r="I50" s="32">
         <v>9.78</v>
       </c>
-      <c r="J50" s="31">
+      <c r="J50" s="32">
         <v>9.1</v>
       </c>
-      <c r="K50" s="31">
+      <c r="K50" s="32">
         <v>7.1</v>
       </c>
-      <c r="L50" s="31">
+      <c r="L50" s="32">
         <v>5.82</v>
       </c>
-      <c r="M50" s="31">
+      <c r="M50" s="32">
         <v>9.93</v>
       </c>
-      <c r="N50" s="31">
+      <c r="N50" s="32">
         <v>8.86</v>
       </c>
-      <c r="O50" s="31">
+      <c r="O50" s="32">
         <v>8.74</v>
       </c>
-      <c r="P50" s="31">
+      <c r="P50" s="32">
         <v>10.97</v>
       </c>
-      <c r="Q50" s="31">
+      <c r="Q50" s="32">
         <v>8.01</v>
       </c>
-      <c r="R50" s="31">
+      <c r="R50" s="32">
         <v>5.16</v>
       </c>
-      <c r="S50" s="31">
+      <c r="S50" s="32">
         <v>5.43</v>
       </c>
-      <c r="T50" s="31">
+      <c r="T50" s="32">
         <v>9.09</v>
       </c>
-      <c r="U50" s="31">
+      <c r="U50" s="32">
         <v>8.11</v>
       </c>
-      <c r="V50" s="31">
+      <c r="V50" s="32">
         <v>4.69</v>
       </c>
-      <c r="W50" s="31">
+      <c r="W50" s="32">
         <v>9.92</v>
       </c>
-      <c r="X50" s="31">
+      <c r="X50" s="32">
         <v>3.04</v>
       </c>
-      <c r="Y50" s="31">
+      <c r="Y50" s="32">
         <v>7.31</v>
       </c>
-      <c r="Z50" s="31">
+      <c r="Z50" s="32">
         <v>3.72</v>
       </c>
-      <c r="AA50" s="31">
+      <c r="AA50" s="32">
         <v>2.36</v>
       </c>
-      <c r="AB50" s="31">
+      <c r="AB50" s="32">
         <v>2.01</v>
       </c>
     </row>
     <row r="51" ht="15.0" customHeight="1">
-      <c r="A51" s="28" t="s">
-        <v>497</v>
-      </c>
-      <c r="B51" s="31">
+      <c r="A51" s="29" t="s">
+        <v>500</v>
+      </c>
+      <c r="B51" s="32">
         <v>4.94</v>
       </c>
-      <c r="C51" s="31">
+      <c r="C51" s="32">
         <v>5.17</v>
       </c>
-      <c r="D51" s="31">
+      <c r="D51" s="32">
         <v>5.97</v>
       </c>
-      <c r="E51" s="31">
+      <c r="E51" s="32">
         <v>7.05</v>
       </c>
-      <c r="F51" s="31">
+      <c r="F51" s="32">
         <v>7.71</v>
       </c>
-      <c r="G51" s="31">
+      <c r="G51" s="32">
         <v>7.85</v>
       </c>
-      <c r="H51" s="31">
+      <c r="H51" s="32">
         <v>8.2</v>
       </c>
-      <c r="I51" s="31">
+      <c r="I51" s="32">
         <v>8.2</v>
       </c>
-      <c r="J51" s="31">
+      <c r="J51" s="32">
         <v>7.92</v>
       </c>
-      <c r="K51" s="31">
+      <c r="K51" s="32">
         <v>7.79</v>
       </c>
-      <c r="L51" s="31">
+      <c r="L51" s="32">
         <v>8.56</v>
       </c>
-      <c r="M51" s="31">
+      <c r="M51" s="32">
         <v>9.28</v>
       </c>
-      <c r="N51" s="31">
+      <c r="N51" s="32">
         <v>8.34</v>
       </c>
-      <c r="O51" s="31">
+      <c r="O51" s="32">
         <v>7.43</v>
       </c>
-      <c r="P51" s="31">
+      <c r="P51" s="32">
         <v>7.47</v>
       </c>
-      <c r="Q51" s="31">
+      <c r="Q51" s="32">
         <v>6.99</v>
       </c>
-      <c r="R51" s="31">
+      <c r="R51" s="32">
         <v>6.29</v>
       </c>
-      <c r="S51" s="31">
+      <c r="S51" s="32">
         <v>6.86</v>
       </c>
-      <c r="T51" s="31">
+      <c r="T51" s="32">
         <v>6.36</v>
       </c>
-      <c r="U51" s="31">
+      <c r="U51" s="32">
         <v>5.88</v>
       </c>
-      <c r="V51" s="31">
+      <c r="V51" s="32">
         <v>4.99</v>
       </c>
-      <c r="W51" s="31">
+      <c r="W51" s="32">
         <v>4.51</v>
       </c>
-      <c r="X51" s="31">
+      <c r="X51" s="32">
         <v>3.25</v>
       </c>
-      <c r="Y51" s="30"/>
-      <c r="Z51" s="30"/>
-      <c r="AA51" s="30"/>
-      <c r="AB51" s="30"/>
+      <c r="Y51" s="31"/>
+      <c r="Z51" s="31"/>
+      <c r="AA51" s="31"/>
+      <c r="AB51" s="31"/>
     </row>
     <row r="52" ht="15.0" customHeight="1">
-      <c r="A52" s="26" t="s">
-        <v>498</v>
-      </c>
-      <c r="B52" s="27"/>
-      <c r="C52" s="27"/>
-      <c r="D52" s="27"/>
-      <c r="E52" s="27"/>
-      <c r="F52" s="27"/>
-      <c r="G52" s="27"/>
-      <c r="H52" s="27"/>
-      <c r="I52" s="27"/>
-      <c r="J52" s="27"/>
-      <c r="K52" s="27"/>
-      <c r="L52" s="27"/>
-      <c r="M52" s="27"/>
-      <c r="N52" s="27"/>
-      <c r="O52" s="27"/>
-      <c r="P52" s="27"/>
-      <c r="Q52" s="27"/>
-      <c r="R52" s="27"/>
-      <c r="S52" s="27"/>
-      <c r="T52" s="27"/>
-      <c r="U52" s="27"/>
-      <c r="V52" s="27"/>
-      <c r="W52" s="27"/>
-      <c r="X52" s="27"/>
-      <c r="Y52" s="27"/>
-      <c r="Z52" s="27"/>
-      <c r="AA52" s="27"/>
-      <c r="AB52" s="27"/>
+      <c r="A52" s="27" t="s">
+        <v>501</v>
+      </c>
+      <c r="B52" s="28"/>
+      <c r="C52" s="28"/>
+      <c r="D52" s="28"/>
+      <c r="E52" s="28"/>
+      <c r="F52" s="28"/>
+      <c r="G52" s="28"/>
+      <c r="H52" s="28"/>
+      <c r="I52" s="28"/>
+      <c r="J52" s="28"/>
+      <c r="K52" s="28"/>
+      <c r="L52" s="28"/>
+      <c r="M52" s="28"/>
+      <c r="N52" s="28"/>
+      <c r="O52" s="28"/>
+      <c r="P52" s="28"/>
+      <c r="Q52" s="28"/>
+      <c r="R52" s="28"/>
+      <c r="S52" s="28"/>
+      <c r="T52" s="28"/>
+      <c r="U52" s="28"/>
+      <c r="V52" s="28"/>
+      <c r="W52" s="28"/>
+      <c r="X52" s="28"/>
+      <c r="Y52" s="28"/>
+      <c r="Z52" s="28"/>
+      <c r="AA52" s="28"/>
+      <c r="AB52" s="28"/>
     </row>
     <row r="53" ht="15.0" customHeight="1">
-      <c r="A53" s="28" t="s">
-        <v>499</v>
-      </c>
-      <c r="B53" s="31">
+      <c r="A53" s="29" t="s">
+        <v>502</v>
+      </c>
+      <c r="B53" s="32">
         <v>23.94</v>
       </c>
-      <c r="C53" s="31">
+      <c r="C53" s="32">
         <v>11.55</v>
       </c>
-      <c r="D53" s="31">
+      <c r="D53" s="32">
         <v>9.03</v>
       </c>
-      <c r="E53" s="31">
+      <c r="E53" s="32">
         <v>12.54</v>
       </c>
-      <c r="F53" s="31">
+      <c r="F53" s="32">
         <v>24.21</v>
       </c>
-      <c r="G53" s="31">
+      <c r="G53" s="32">
         <v>14.71</v>
       </c>
-      <c r="H53" s="31">
+      <c r="H53" s="32">
         <v>17.29</v>
       </c>
-      <c r="I53" s="31">
+      <c r="I53" s="32">
         <v>15.77</v>
       </c>
-      <c r="J53" s="31">
+      <c r="J53" s="32">
         <v>15.77</v>
       </c>
-      <c r="K53" s="31">
+      <c r="K53" s="32">
         <v>11.57</v>
       </c>
-      <c r="L53" s="31">
+      <c r="L53" s="32">
         <v>9.37</v>
       </c>
-      <c r="M53" s="31">
+      <c r="M53" s="32">
         <v>22.46</v>
       </c>
-      <c r="N53" s="31">
+      <c r="N53" s="32">
         <v>16.58</v>
       </c>
-      <c r="O53" s="31">
+      <c r="O53" s="32">
         <v>14.14</v>
       </c>
-      <c r="P53" s="31">
+      <c r="P53" s="32">
         <v>19.62</v>
       </c>
-      <c r="Q53" s="31">
+      <c r="Q53" s="32">
         <v>15.4</v>
       </c>
-      <c r="R53" s="31">
+      <c r="R53" s="32">
         <v>12.75</v>
       </c>
-      <c r="S53" s="31">
+      <c r="S53" s="32">
         <v>7.92</v>
       </c>
-      <c r="T53" s="31">
+      <c r="T53" s="32">
         <v>19.77</v>
       </c>
-      <c r="U53" s="31">
+      <c r="U53" s="32">
         <v>14.42</v>
       </c>
-      <c r="V53" s="31">
+      <c r="V53" s="32">
         <v>7.75</v>
       </c>
-      <c r="W53" s="31">
+      <c r="W53" s="32">
         <v>84.93</v>
       </c>
-      <c r="X53" s="31">
+      <c r="X53" s="32">
         <v>4.87</v>
       </c>
-      <c r="Y53" s="30"/>
-      <c r="Z53" s="31">
+      <c r="Y53" s="31"/>
+      <c r="Z53" s="32">
         <v>12.47</v>
       </c>
-      <c r="AA53" s="31">
+      <c r="AA53" s="32">
         <v>5.27</v>
       </c>
-      <c r="AB53" s="31">
+      <c r="AB53" s="32">
         <v>7.61</v>
       </c>
     </row>
     <row r="54" ht="15.0" customHeight="1">
-      <c r="A54" s="28" t="s">
-        <v>500</v>
-      </c>
-      <c r="B54" s="31">
+      <c r="A54" s="29" t="s">
+        <v>503</v>
+      </c>
+      <c r="B54" s="32">
         <v>13.46</v>
       </c>
-      <c r="C54" s="31">
+      <c r="C54" s="32">
         <v>13.0</v>
       </c>
-      <c r="D54" s="31">
+      <c r="D54" s="32">
         <v>13.87</v>
       </c>
-      <c r="E54" s="31">
+      <c r="E54" s="32">
         <v>15.82</v>
       </c>
-      <c r="F54" s="31">
+      <c r="F54" s="32">
         <v>17.01</v>
       </c>
-      <c r="G54" s="31">
+      <c r="G54" s="32">
         <v>14.84</v>
       </c>
-      <c r="H54" s="31">
+      <c r="H54" s="32">
         <v>13.71</v>
       </c>
-      <c r="I54" s="31">
+      <c r="I54" s="32">
         <v>13.97</v>
       </c>
-      <c r="J54" s="31">
+      <c r="J54" s="32">
         <v>13.89</v>
       </c>
-      <c r="K54" s="31">
+      <c r="K54" s="32">
         <v>13.51</v>
       </c>
-      <c r="L54" s="31">
+      <c r="L54" s="32">
         <v>15.21</v>
       </c>
-      <c r="M54" s="31">
+      <c r="M54" s="32">
         <v>17.3</v>
       </c>
-      <c r="N54" s="31">
+      <c r="N54" s="32">
         <v>15.79</v>
       </c>
-      <c r="O54" s="31">
+      <c r="O54" s="32">
         <v>13.03</v>
       </c>
-      <c r="P54" s="31">
+      <c r="P54" s="32">
         <v>13.8</v>
       </c>
-      <c r="Q54" s="31">
+      <c r="Q54" s="32">
         <v>12.88</v>
       </c>
-      <c r="R54" s="31">
+      <c r="R54" s="32">
         <v>11.21</v>
       </c>
-      <c r="S54" s="31">
+      <c r="S54" s="32">
         <v>12.61</v>
       </c>
-      <c r="T54" s="31">
+      <c r="T54" s="32">
         <v>12.19</v>
       </c>
-      <c r="U54" s="31">
+      <c r="U54" s="32">
         <v>12.4</v>
       </c>
-      <c r="V54" s="31">
+      <c r="V54" s="32">
         <v>11.71</v>
       </c>
-      <c r="W54" s="31">
+      <c r="W54" s="32">
         <v>12.5</v>
       </c>
-      <c r="X54" s="31">
+      <c r="X54" s="32">
         <v>8.5</v>
       </c>
-      <c r="Y54" s="30"/>
-      <c r="Z54" s="30"/>
-      <c r="AA54" s="30"/>
-      <c r="AB54" s="30"/>
+      <c r="Y54" s="31"/>
+      <c r="Z54" s="31"/>
+      <c r="AA54" s="31"/>
+      <c r="AB54" s="31"/>
     </row>
     <row r="55" ht="15.0" customHeight="1">
-      <c r="A55" s="26" t="s">
-        <v>501</v>
-      </c>
-      <c r="B55" s="27"/>
-      <c r="C55" s="27"/>
-      <c r="D55" s="27"/>
-      <c r="E55" s="27"/>
-      <c r="F55" s="27"/>
-      <c r="G55" s="27"/>
-      <c r="H55" s="27"/>
-      <c r="I55" s="27"/>
-      <c r="J55" s="27"/>
-      <c r="K55" s="27"/>
-      <c r="L55" s="27"/>
-      <c r="M55" s="27"/>
-      <c r="N55" s="27"/>
-      <c r="O55" s="27"/>
-      <c r="P55" s="27"/>
-      <c r="Q55" s="27"/>
-      <c r="R55" s="27"/>
-      <c r="S55" s="27"/>
-      <c r="T55" s="27"/>
-      <c r="U55" s="27"/>
-      <c r="V55" s="27"/>
-      <c r="W55" s="27"/>
-      <c r="X55" s="27"/>
-      <c r="Y55" s="27"/>
-      <c r="Z55" s="27"/>
-      <c r="AA55" s="27"/>
-      <c r="AB55" s="27"/>
+      <c r="A55" s="27" t="s">
+        <v>504</v>
+      </c>
+      <c r="B55" s="28"/>
+      <c r="C55" s="28"/>
+      <c r="D55" s="28"/>
+      <c r="E55" s="28"/>
+      <c r="F55" s="28"/>
+      <c r="G55" s="28"/>
+      <c r="H55" s="28"/>
+      <c r="I55" s="28"/>
+      <c r="J55" s="28"/>
+      <c r="K55" s="28"/>
+      <c r="L55" s="28"/>
+      <c r="M55" s="28"/>
+      <c r="N55" s="28"/>
+      <c r="O55" s="28"/>
+      <c r="P55" s="28"/>
+      <c r="Q55" s="28"/>
+      <c r="R55" s="28"/>
+      <c r="S55" s="28"/>
+      <c r="T55" s="28"/>
+      <c r="U55" s="28"/>
+      <c r="V55" s="28"/>
+      <c r="W55" s="28"/>
+      <c r="X55" s="28"/>
+      <c r="Y55" s="28"/>
+      <c r="Z55" s="28"/>
+      <c r="AA55" s="28"/>
+      <c r="AB55" s="28"/>
     </row>
     <row r="56" ht="15.0" customHeight="1">
-      <c r="A56" s="28" t="s">
-        <v>502</v>
-      </c>
-      <c r="B56" s="31">
+      <c r="A56" s="29" t="s">
+        <v>505</v>
+      </c>
+      <c r="B56" s="32">
         <v>9.33</v>
       </c>
-      <c r="C56" s="31">
+      <c r="C56" s="32">
         <v>11.67</v>
       </c>
-      <c r="D56" s="31">
+      <c r="D56" s="32">
         <v>9.03</v>
       </c>
-      <c r="E56" s="31">
+      <c r="E56" s="32">
         <v>10.75</v>
       </c>
-      <c r="F56" s="31">
+      <c r="F56" s="32">
         <v>24.13</v>
       </c>
-      <c r="G56" s="31">
+      <c r="G56" s="32">
         <v>14.99</v>
       </c>
-      <c r="H56" s="31">
+      <c r="H56" s="32">
         <v>12.92</v>
       </c>
-      <c r="I56" s="31">
+      <c r="I56" s="32">
         <v>16.06</v>
       </c>
-      <c r="J56" s="31">
+      <c r="J56" s="32">
         <v>15.77</v>
       </c>
-      <c r="K56" s="31">
+      <c r="K56" s="32">
         <v>10.84</v>
       </c>
-      <c r="L56" s="31">
+      <c r="L56" s="32">
         <v>9.42</v>
       </c>
-      <c r="M56" s="31">
+      <c r="M56" s="32">
         <v>22.46</v>
       </c>
-      <c r="N56" s="31">
+      <c r="N56" s="32">
         <v>17.69</v>
       </c>
-      <c r="O56" s="31">
+      <c r="O56" s="32">
         <v>14.14</v>
       </c>
-      <c r="P56" s="31">
+      <c r="P56" s="32">
         <v>19.62</v>
       </c>
-      <c r="Q56" s="31">
+      <c r="Q56" s="32">
         <v>16.48</v>
       </c>
-      <c r="R56" s="31">
+      <c r="R56" s="32">
         <v>13.45</v>
       </c>
-      <c r="S56" s="31">
+      <c r="S56" s="32">
         <v>8.35</v>
       </c>
-      <c r="T56" s="31">
+      <c r="T56" s="32">
         <v>19.77</v>
       </c>
-      <c r="U56" s="31">
+      <c r="U56" s="32">
         <v>14.42</v>
       </c>
-      <c r="V56" s="31">
+      <c r="V56" s="32">
         <v>9.55</v>
       </c>
-      <c r="W56" s="31">
+      <c r="W56" s="32">
         <v>10.6</v>
       </c>
-      <c r="X56" s="31">
+      <c r="X56" s="32">
         <v>11.59</v>
       </c>
-      <c r="Y56" s="31">
+      <c r="Y56" s="32">
         <v>8.32</v>
       </c>
-      <c r="Z56" s="31">
+      <c r="Z56" s="32">
         <v>11.75</v>
       </c>
-      <c r="AA56" s="31">
+      <c r="AA56" s="32">
         <v>43.24</v>
       </c>
-      <c r="AB56" s="31">
+      <c r="AB56" s="32">
         <v>10.71</v>
       </c>
     </row>
     <row r="57" ht="15.0" customHeight="1">
-      <c r="A57" s="28" t="s">
-        <v>503</v>
-      </c>
-      <c r="B57" s="31">
+      <c r="A57" s="29" t="s">
+        <v>506</v>
+      </c>
+      <c r="B57" s="32">
         <v>1.77</v>
       </c>
-      <c r="C57" s="31">
+      <c r="C57" s="32">
         <v>2.0</v>
       </c>
-      <c r="D57" s="31">
+      <c r="D57" s="32">
         <v>2.17</v>
       </c>
-      <c r="E57" s="31">
+      <c r="E57" s="32">
         <v>2.37</v>
       </c>
-      <c r="F57" s="31">
+      <c r="F57" s="32">
         <v>2.25</v>
       </c>
-      <c r="G57" s="31">
+      <c r="G57" s="32">
         <v>2.24</v>
       </c>
-      <c r="H57" s="31">
+      <c r="H57" s="32">
         <v>2.19</v>
       </c>
-      <c r="I57" s="31">
+      <c r="I57" s="32">
         <v>2.13</v>
       </c>
-      <c r="J57" s="31">
+      <c r="J57" s="32">
         <v>1.99</v>
       </c>
-      <c r="K57" s="31">
+      <c r="K57" s="32">
         <v>1.95</v>
       </c>
-      <c r="L57" s="31">
+      <c r="L57" s="32">
         <v>2.01</v>
       </c>
-      <c r="M57" s="31">
+      <c r="M57" s="32">
         <v>2.07</v>
       </c>
-      <c r="N57" s="31">
+      <c r="N57" s="32">
         <v>2.46</v>
       </c>
-      <c r="O57" s="31">
+      <c r="O57" s="32">
         <v>2.51</v>
       </c>
-      <c r="P57" s="31">
+      <c r="P57" s="32">
         <v>2.67</v>
       </c>
-      <c r="Q57" s="31">
+      <c r="Q57" s="32">
         <v>2.63</v>
       </c>
-      <c r="R57" s="31">
+      <c r="R57" s="32">
         <v>2.66</v>
       </c>
-      <c r="S57" s="31">
+      <c r="S57" s="32">
         <v>2.17</v>
       </c>
-      <c r="T57" s="31">
+      <c r="T57" s="32">
         <v>1.91</v>
       </c>
-      <c r="U57" s="31">
+      <c r="U57" s="32">
         <v>1.58</v>
       </c>
-      <c r="V57" s="31">
+      <c r="V57" s="32">
         <v>1.19</v>
       </c>
-      <c r="W57" s="31">
+      <c r="W57" s="32">
         <v>0.9</v>
       </c>
-      <c r="X57" s="31">
+      <c r="X57" s="32">
         <v>0.63</v>
       </c>
-      <c r="Y57" s="30"/>
-      <c r="Z57" s="30"/>
-      <c r="AA57" s="30"/>
-      <c r="AB57" s="30"/>
+      <c r="Y57" s="31"/>
+      <c r="Z57" s="31"/>
+      <c r="AA57" s="31"/>
+      <c r="AB57" s="31"/>
     </row>
     <row r="58" ht="15.0" customHeight="1">
-      <c r="A58" s="26" t="s">
-        <v>504</v>
-      </c>
-      <c r="B58" s="27"/>
-      <c r="C58" s="27"/>
-      <c r="D58" s="27"/>
-      <c r="E58" s="27"/>
-      <c r="F58" s="27"/>
-      <c r="G58" s="27"/>
-      <c r="H58" s="27"/>
-      <c r="I58" s="27"/>
-      <c r="J58" s="27"/>
-      <c r="K58" s="27"/>
-      <c r="L58" s="27"/>
-      <c r="M58" s="27"/>
-      <c r="N58" s="27"/>
-      <c r="O58" s="27"/>
-      <c r="P58" s="27"/>
-      <c r="Q58" s="27"/>
-      <c r="R58" s="27"/>
-      <c r="S58" s="27"/>
-      <c r="T58" s="27"/>
-      <c r="U58" s="27"/>
-      <c r="V58" s="27"/>
-      <c r="W58" s="27"/>
-      <c r="X58" s="27"/>
-      <c r="Y58" s="27"/>
-      <c r="Z58" s="27"/>
-      <c r="AA58" s="27"/>
-      <c r="AB58" s="27"/>
+      <c r="A58" s="27" t="s">
+        <v>507</v>
+      </c>
+      <c r="B58" s="28"/>
+      <c r="C58" s="28"/>
+      <c r="D58" s="28"/>
+      <c r="E58" s="28"/>
+      <c r="F58" s="28"/>
+      <c r="G58" s="28"/>
+      <c r="H58" s="28"/>
+      <c r="I58" s="28"/>
+      <c r="J58" s="28"/>
+      <c r="K58" s="28"/>
+      <c r="L58" s="28"/>
+      <c r="M58" s="28"/>
+      <c r="N58" s="28"/>
+      <c r="O58" s="28"/>
+      <c r="P58" s="28"/>
+      <c r="Q58" s="28"/>
+      <c r="R58" s="28"/>
+      <c r="S58" s="28"/>
+      <c r="T58" s="28"/>
+      <c r="U58" s="28"/>
+      <c r="V58" s="28"/>
+      <c r="W58" s="28"/>
+      <c r="X58" s="28"/>
+      <c r="Y58" s="28"/>
+      <c r="Z58" s="28"/>
+      <c r="AA58" s="28"/>
+      <c r="AB58" s="28"/>
     </row>
     <row r="59" ht="15.0" customHeight="1">
-      <c r="A59" s="28" t="s">
-        <v>505</v>
-      </c>
-      <c r="B59" s="34">
+      <c r="A59" s="29" t="s">
+        <v>508</v>
+      </c>
+      <c r="B59" s="35">
         <v>-0.39</v>
       </c>
-      <c r="C59" s="34">
+      <c r="C59" s="35">
         <v>-0.27</v>
       </c>
-      <c r="D59" s="31">
+      <c r="D59" s="32">
         <v>45.98</v>
       </c>
-      <c r="E59" s="31">
+      <c r="E59" s="32">
         <v>0.08</v>
       </c>
-      <c r="F59" s="34">
+      <c r="F59" s="35">
         <v>-0.73</v>
       </c>
-      <c r="G59" s="31">
+      <c r="G59" s="32">
         <v>1.18</v>
       </c>
-      <c r="H59" s="34">
+      <c r="H59" s="35">
         <v>-0.63</v>
       </c>
-      <c r="I59" s="31">
+      <c r="I59" s="32">
         <v>0.71</v>
       </c>
-      <c r="J59" s="34">
+      <c r="J59" s="35">
         <v>-0.79</v>
       </c>
-      <c r="K59" s="31">
+      <c r="K59" s="32">
         <v>1.73</v>
       </c>
-      <c r="L59" s="31">
+      <c r="L59" s="32">
         <v>0.07</v>
       </c>
-      <c r="M59" s="34">
+      <c r="M59" s="35">
         <v>-0.88</v>
       </c>
-      <c r="N59" s="34">
+      <c r="N59" s="35">
         <v>-1.08</v>
       </c>
-      <c r="O59" s="31">
+      <c r="O59" s="32">
         <v>0.69</v>
       </c>
-      <c r="P59" s="31">
+      <c r="P59" s="32">
         <v>1.99</v>
       </c>
-      <c r="Q59" s="31">
+      <c r="Q59" s="32">
         <v>0.73</v>
       </c>
-      <c r="R59" s="34">
+      <c r="R59" s="35">
         <v>-0.21</v>
       </c>
-      <c r="S59" s="31">
+      <c r="S59" s="32">
         <v>0.06</v>
       </c>
-      <c r="T59" s="34">
+      <c r="T59" s="35">
         <v>-0.7</v>
       </c>
-      <c r="U59" s="34">
+      <c r="U59" s="35">
         <v>-0.53</v>
       </c>
-      <c r="V59" s="31">
+      <c r="V59" s="32">
         <v>0.01</v>
       </c>
-      <c r="W59" s="34">
+      <c r="W59" s="35">
         <v>-0.93</v>
       </c>
-      <c r="X59" s="31">
+      <c r="X59" s="32">
         <v>0.01</v>
       </c>
-      <c r="Y59" s="30"/>
-      <c r="Z59" s="34">
+      <c r="Y59" s="31"/>
+      <c r="Z59" s="35">
         <v>-0.24</v>
       </c>
-      <c r="AA59" s="31">
+      <c r="AA59" s="32">
         <v>0.04</v>
       </c>
-      <c r="AB59" s="30"/>
+      <c r="AB59" s="31"/>
     </row>
     <row r="60" ht="15.0" customHeight="1">
-      <c r="A60" s="28" t="s">
-        <v>506</v>
-      </c>
-      <c r="B60" s="34">
+      <c r="A60" s="29" t="s">
+        <v>509</v>
+      </c>
+      <c r="B60" s="35">
         <v>-0.79</v>
       </c>
-      <c r="C60" s="31">
+      <c r="C60" s="32">
         <v>5.46</v>
       </c>
-      <c r="D60" s="31">
+      <c r="D60" s="32">
         <v>1.87</v>
       </c>
-      <c r="E60" s="31">
+      <c r="E60" s="32">
         <v>1.34</v>
       </c>
-      <c r="F60" s="34">
+      <c r="F60" s="35">
         <v>-1.45</v>
       </c>
-      <c r="G60" s="34">
+      <c r="G60" s="35">
         <v>-4.73</v>
       </c>
-      <c r="H60" s="31">
+      <c r="H60" s="32">
         <v>1.2</v>
       </c>
-      <c r="I60" s="31">
+      <c r="I60" s="32">
         <v>1.16</v>
       </c>
-      <c r="J60" s="31">
+      <c r="J60" s="32">
         <v>3.43</v>
       </c>
-      <c r="K60" s="31">
+      <c r="K60" s="32">
         <v>1.05</v>
       </c>
-      <c r="L60" s="31">
+      <c r="L60" s="32">
         <v>1.12</v>
       </c>
-      <c r="M60" s="31">
+      <c r="M60" s="32">
         <v>68.36</v>
       </c>
-      <c r="N60" s="34">
+      <c r="N60" s="35">
         <v>-1.32</v>
       </c>
-      <c r="O60" s="31">
+      <c r="O60" s="32">
         <v>1.61</v>
       </c>
-      <c r="P60" s="34">
+      <c r="P60" s="35">
         <v>-5.44</v>
       </c>
-      <c r="Q60" s="34">
+      <c r="Q60" s="35">
         <v>-1.26</v>
       </c>
-      <c r="R60" s="31">
+      <c r="R60" s="32">
         <v>0.25</v>
       </c>
-      <c r="S60" s="31">
+      <c r="S60" s="32">
         <v>2.15</v>
       </c>
-      <c r="T60" s="30"/>
-      <c r="U60" s="31">
+      <c r="T60" s="31"/>
+      <c r="U60" s="32">
         <v>0.43</v>
       </c>
-      <c r="V60" s="31">
+      <c r="V60" s="32">
         <v>0.63</v>
       </c>
-      <c r="W60" s="34">
+      <c r="W60" s="35">
         <v>-0.74</v>
       </c>
-      <c r="X60" s="30"/>
-      <c r="Y60" s="30"/>
-      <c r="Z60" s="30"/>
-      <c r="AA60" s="30"/>
-      <c r="AB60" s="30"/>
+      <c r="X60" s="31"/>
+      <c r="Y60" s="31"/>
+      <c r="Z60" s="31"/>
+      <c r="AA60" s="31"/>
+      <c r="AB60" s="31"/>
     </row>
     <row r="61" ht="15.0" customHeight="1">
-      <c r="A61" s="26" t="s">
-        <v>507</v>
-      </c>
-      <c r="B61" s="27"/>
-      <c r="C61" s="27"/>
-      <c r="D61" s="27"/>
-      <c r="E61" s="27"/>
-      <c r="F61" s="27"/>
-      <c r="G61" s="27"/>
-      <c r="H61" s="27"/>
-      <c r="I61" s="27"/>
-      <c r="J61" s="27"/>
-      <c r="K61" s="27"/>
-      <c r="L61" s="27"/>
-      <c r="M61" s="27"/>
-      <c r="N61" s="27"/>
-      <c r="O61" s="27"/>
-      <c r="P61" s="27"/>
-      <c r="Q61" s="27"/>
-      <c r="R61" s="27"/>
-      <c r="S61" s="27"/>
-      <c r="T61" s="27"/>
-      <c r="U61" s="27"/>
-      <c r="V61" s="27"/>
-      <c r="W61" s="27"/>
-      <c r="X61" s="27"/>
-      <c r="Y61" s="27"/>
-      <c r="Z61" s="27"/>
-      <c r="AA61" s="27"/>
-      <c r="AB61" s="27"/>
+      <c r="A61" s="27" t="s">
+        <v>510</v>
+      </c>
+      <c r="B61" s="28"/>
+      <c r="C61" s="28"/>
+      <c r="D61" s="28"/>
+      <c r="E61" s="28"/>
+      <c r="F61" s="28"/>
+      <c r="G61" s="28"/>
+      <c r="H61" s="28"/>
+      <c r="I61" s="28"/>
+      <c r="J61" s="28"/>
+      <c r="K61" s="28"/>
+      <c r="L61" s="28"/>
+      <c r="M61" s="28"/>
+      <c r="N61" s="28"/>
+      <c r="O61" s="28"/>
+      <c r="P61" s="28"/>
+      <c r="Q61" s="28"/>
+      <c r="R61" s="28"/>
+      <c r="S61" s="28"/>
+      <c r="T61" s="28"/>
+      <c r="U61" s="28"/>
+      <c r="V61" s="28"/>
+      <c r="W61" s="28"/>
+      <c r="X61" s="28"/>
+      <c r="Y61" s="28"/>
+      <c r="Z61" s="28"/>
+      <c r="AA61" s="28"/>
+      <c r="AB61" s="28"/>
     </row>
     <row r="62" ht="15.0" customHeight="1">
-      <c r="A62" s="28" t="s">
-        <v>508</v>
-      </c>
-      <c r="B62" s="31">
+      <c r="A62" s="29" t="s">
+        <v>511</v>
+      </c>
+      <c r="B62" s="32">
         <v>0.62</v>
       </c>
-      <c r="C62" s="31">
+      <c r="C62" s="32">
         <v>0.66</v>
       </c>
-      <c r="D62" s="31">
+      <c r="D62" s="32">
         <v>0.76</v>
       </c>
-      <c r="E62" s="31">
+      <c r="E62" s="32">
         <v>0.91</v>
       </c>
-      <c r="F62" s="31">
+      <c r="F62" s="32">
         <v>0.91</v>
       </c>
-      <c r="G62" s="31">
+      <c r="G62" s="32">
         <v>0.74</v>
       </c>
-      <c r="H62" s="31">
+      <c r="H62" s="32">
         <v>0.8</v>
       </c>
-      <c r="I62" s="31">
+      <c r="I62" s="32">
         <v>0.85</v>
       </c>
-      <c r="J62" s="31">
+      <c r="J62" s="32">
         <v>0.78</v>
       </c>
-      <c r="K62" s="31">
+      <c r="K62" s="32">
         <v>0.75</v>
       </c>
-      <c r="L62" s="31">
+      <c r="L62" s="32">
         <v>0.58</v>
       </c>
-      <c r="M62" s="31">
+      <c r="M62" s="32">
         <v>0.61</v>
       </c>
-      <c r="N62" s="31">
+      <c r="N62" s="32">
         <v>0.63</v>
       </c>
-      <c r="O62" s="31">
+      <c r="O62" s="32">
         <v>0.59</v>
       </c>
-      <c r="P62" s="31">
+      <c r="P62" s="32">
         <v>0.7</v>
       </c>
-      <c r="Q62" s="31">
+      <c r="Q62" s="32">
         <v>0.63</v>
       </c>
-      <c r="R62" s="31">
+      <c r="R62" s="32">
         <v>0.49</v>
       </c>
-      <c r="S62" s="31">
+      <c r="S62" s="32">
         <v>0.89</v>
       </c>
-      <c r="T62" s="31">
+      <c r="T62" s="32">
         <v>0.86</v>
       </c>
-      <c r="U62" s="31">
+      <c r="U62" s="32">
         <v>0.87</v>
       </c>
-      <c r="V62" s="31">
+      <c r="V62" s="32">
         <v>0.62</v>
       </c>
-      <c r="W62" s="31">
+      <c r="W62" s="32">
         <v>0.77</v>
       </c>
-      <c r="X62" s="31">
+      <c r="X62" s="32">
         <v>0.53</v>
       </c>
-      <c r="Y62" s="31">
+      <c r="Y62" s="32">
         <v>0.53</v>
       </c>
-      <c r="Z62" s="31">
+      <c r="Z62" s="32">
         <v>0.55</v>
       </c>
-      <c r="AA62" s="31">
+      <c r="AA62" s="32">
         <v>2.66</v>
       </c>
-      <c r="AB62" s="31">
+      <c r="AB62" s="32">
         <v>0.35</v>
       </c>
     </row>
     <row r="63" ht="15.0" customHeight="1">
-      <c r="A63" s="28" t="s">
-        <v>509</v>
-      </c>
-      <c r="B63" s="31">
+      <c r="A63" s="29" t="s">
+        <v>512</v>
+      </c>
+      <c r="B63" s="32">
         <v>0.77</v>
       </c>
-      <c r="C63" s="31">
+      <c r="C63" s="32">
         <v>0.79</v>
       </c>
-      <c r="D63" s="31">
+      <c r="D63" s="32">
         <v>0.82</v>
       </c>
-      <c r="E63" s="31">
+      <c r="E63" s="32">
         <v>0.84</v>
       </c>
-      <c r="F63" s="31">
+      <c r="F63" s="32">
         <v>0.81</v>
       </c>
-      <c r="G63" s="31">
+      <c r="G63" s="32">
         <v>0.78</v>
       </c>
-      <c r="H63" s="31">
+      <c r="H63" s="32">
         <v>0.75</v>
       </c>
-      <c r="I63" s="31">
+      <c r="I63" s="32">
         <v>0.71</v>
       </c>
-      <c r="J63" s="31">
+      <c r="J63" s="32">
         <v>0.67</v>
       </c>
-      <c r="K63" s="31">
+      <c r="K63" s="32">
         <v>0.63</v>
       </c>
-      <c r="L63" s="31">
+      <c r="L63" s="32">
         <v>0.62</v>
       </c>
-      <c r="M63" s="31">
+      <c r="M63" s="32">
         <v>0.63</v>
       </c>
-      <c r="N63" s="31">
+      <c r="N63" s="32">
         <v>0.61</v>
       </c>
-      <c r="O63" s="31">
+      <c r="O63" s="32">
         <v>0.64</v>
       </c>
-      <c r="P63" s="31">
+      <c r="P63" s="32">
         <v>0.69</v>
       </c>
-      <c r="Q63" s="31">
+      <c r="Q63" s="32">
         <v>0.71</v>
       </c>
-      <c r="R63" s="31">
+      <c r="R63" s="32">
         <v>0.72</v>
       </c>
-      <c r="S63" s="31">
+      <c r="S63" s="32">
         <v>0.81</v>
       </c>
-      <c r="T63" s="31">
+      <c r="T63" s="32">
         <v>0.75</v>
       </c>
-      <c r="U63" s="31">
+      <c r="U63" s="32">
         <v>0.68</v>
       </c>
-      <c r="V63" s="31">
+      <c r="V63" s="32">
         <v>0.61</v>
       </c>
-      <c r="W63" s="31">
+      <c r="W63" s="32">
         <v>0.89</v>
       </c>
-      <c r="X63" s="31">
+      <c r="X63" s="32">
         <v>0.84</v>
       </c>
-      <c r="Y63" s="30"/>
-      <c r="Z63" s="30"/>
-      <c r="AA63" s="30"/>
-      <c r="AB63" s="30"/>
+      <c r="Y63" s="31"/>
+      <c r="Z63" s="31"/>
+      <c r="AA63" s="31"/>
+      <c r="AB63" s="31"/>
     </row>
     <row r="64" ht="15.0" customHeight="1">
-      <c r="A64" s="26" t="s">
-        <v>510</v>
-      </c>
-      <c r="B64" s="27"/>
-      <c r="C64" s="27"/>
-      <c r="D64" s="27"/>
-      <c r="E64" s="27"/>
-      <c r="F64" s="27"/>
-      <c r="G64" s="27"/>
-      <c r="H64" s="27"/>
-      <c r="I64" s="27"/>
-      <c r="J64" s="27"/>
-      <c r="K64" s="27"/>
-      <c r="L64" s="27"/>
-      <c r="M64" s="27"/>
-      <c r="N64" s="27"/>
-      <c r="O64" s="27"/>
-      <c r="P64" s="27"/>
-      <c r="Q64" s="27"/>
-      <c r="R64" s="27"/>
-      <c r="S64" s="27"/>
-      <c r="T64" s="27"/>
-      <c r="U64" s="27"/>
-      <c r="V64" s="27"/>
-      <c r="W64" s="27"/>
-      <c r="X64" s="27"/>
-      <c r="Y64" s="27"/>
-      <c r="Z64" s="27"/>
-      <c r="AA64" s="27"/>
-      <c r="AB64" s="27"/>
+      <c r="A64" s="27" t="s">
+        <v>513</v>
+      </c>
+      <c r="B64" s="28"/>
+      <c r="C64" s="28"/>
+      <c r="D64" s="28"/>
+      <c r="E64" s="28"/>
+      <c r="F64" s="28"/>
+      <c r="G64" s="28"/>
+      <c r="H64" s="28"/>
+      <c r="I64" s="28"/>
+      <c r="J64" s="28"/>
+      <c r="K64" s="28"/>
+      <c r="L64" s="28"/>
+      <c r="M64" s="28"/>
+      <c r="N64" s="28"/>
+      <c r="O64" s="28"/>
+      <c r="P64" s="28"/>
+      <c r="Q64" s="28"/>
+      <c r="R64" s="28"/>
+      <c r="S64" s="28"/>
+      <c r="T64" s="28"/>
+      <c r="U64" s="28"/>
+      <c r="V64" s="28"/>
+      <c r="W64" s="28"/>
+      <c r="X64" s="28"/>
+      <c r="Y64" s="28"/>
+      <c r="Z64" s="28"/>
+      <c r="AA64" s="28"/>
+      <c r="AB64" s="28"/>
     </row>
     <row r="65" ht="15.0" customHeight="1">
-      <c r="A65" s="28" t="s">
-        <v>511</v>
-      </c>
-      <c r="B65" s="31">
+      <c r="A65" s="29" t="s">
+        <v>514</v>
+      </c>
+      <c r="B65" s="32">
         <v>6.22</v>
       </c>
-      <c r="C65" s="31">
+      <c r="C65" s="32">
         <v>6.26</v>
       </c>
-      <c r="D65" s="31">
+      <c r="D65" s="32">
         <v>5.93</v>
       </c>
-      <c r="E65" s="31">
+      <c r="E65" s="32">
         <v>7.36</v>
       </c>
-      <c r="F65" s="31">
+      <c r="F65" s="32">
         <v>9.5</v>
       </c>
-      <c r="G65" s="31">
+      <c r="G65" s="32">
         <v>8.86</v>
       </c>
-      <c r="H65" s="31">
+      <c r="H65" s="32">
         <v>11.71</v>
       </c>
-      <c r="I65" s="31">
+      <c r="I65" s="32">
         <v>12.67</v>
       </c>
-      <c r="J65" s="31">
+      <c r="J65" s="32">
         <v>11.38</v>
       </c>
-      <c r="K65" s="31">
+      <c r="K65" s="32">
         <v>9.8</v>
       </c>
-      <c r="L65" s="31">
+      <c r="L65" s="32">
         <v>8.17</v>
       </c>
-      <c r="M65" s="31">
+      <c r="M65" s="32">
         <v>13.61</v>
       </c>
-      <c r="N65" s="31">
+      <c r="N65" s="32">
         <v>16.49</v>
       </c>
-      <c r="O65" s="31">
+      <c r="O65" s="32">
         <v>9.6</v>
       </c>
-      <c r="P65" s="31">
+      <c r="P65" s="32">
         <v>10.67</v>
       </c>
-      <c r="Q65" s="31">
+      <c r="Q65" s="32">
         <v>8.86</v>
       </c>
-      <c r="R65" s="31">
+      <c r="R65" s="32">
         <v>6.98</v>
       </c>
-      <c r="S65" s="31">
+      <c r="S65" s="32">
         <v>5.27</v>
       </c>
-      <c r="T65" s="31">
+      <c r="T65" s="32">
         <v>8.7</v>
       </c>
-      <c r="U65" s="31">
+      <c r="U65" s="32">
         <v>6.82</v>
       </c>
-      <c r="V65" s="31">
+      <c r="V65" s="32">
         <v>3.6</v>
       </c>
-      <c r="W65" s="31">
+      <c r="W65" s="32">
         <v>3.76</v>
       </c>
-      <c r="X65" s="31">
+      <c r="X65" s="32">
         <v>7.9</v>
       </c>
-      <c r="Y65" s="31">
+      <c r="Y65" s="32">
         <v>2.73</v>
       </c>
-      <c r="Z65" s="31">
+      <c r="Z65" s="32">
         <v>4.68</v>
       </c>
-      <c r="AA65" s="31">
+      <c r="AA65" s="32">
         <v>58.18</v>
       </c>
-      <c r="AB65" s="31">
+      <c r="AB65" s="32">
         <v>2.64</v>
       </c>
     </row>
     <row r="66" ht="15.0" customHeight="1">
-      <c r="A66" s="28" t="s">
-        <v>512</v>
-      </c>
-      <c r="B66" s="31">
+      <c r="A66" s="29" t="s">
+        <v>515</v>
+      </c>
+      <c r="B66" s="32">
         <v>6.92</v>
       </c>
-      <c r="C66" s="31">
+      <c r="C66" s="32">
         <v>7.38</v>
       </c>
-      <c r="D66" s="31">
+      <c r="D66" s="32">
         <v>8.19</v>
       </c>
-      <c r="E66" s="31">
+      <c r="E66" s="32">
         <v>9.52</v>
       </c>
-      <c r="F66" s="31">
+      <c r="F66" s="32">
         <v>10.59</v>
       </c>
-      <c r="G66" s="31">
+      <c r="G66" s="32">
         <v>10.72</v>
       </c>
-      <c r="H66" s="31">
+      <c r="H66" s="32">
         <v>10.74</v>
       </c>
-      <c r="I66" s="31">
+      <c r="I66" s="32">
         <v>10.91</v>
       </c>
-      <c r="J66" s="31">
+      <c r="J66" s="32">
         <v>11.22</v>
       </c>
-      <c r="K66" s="31">
+      <c r="K66" s="32">
         <v>10.83</v>
       </c>
-      <c r="L66" s="31">
+      <c r="L66" s="32">
         <v>11.07</v>
       </c>
-      <c r="M66" s="31">
+      <c r="M66" s="32">
         <v>11.47</v>
       </c>
-      <c r="N66" s="31">
+      <c r="N66" s="32">
         <v>10.18</v>
       </c>
-      <c r="O66" s="31">
+      <c r="O66" s="32">
         <v>8.11</v>
       </c>
-      <c r="P66" s="31">
+      <c r="P66" s="32">
         <v>7.87</v>
       </c>
-      <c r="Q66" s="31">
+      <c r="Q66" s="32">
         <v>7.12</v>
       </c>
-      <c r="R66" s="31">
+      <c r="R66" s="32">
         <v>6.03</v>
       </c>
-      <c r="S66" s="31">
+      <c r="S66" s="32">
         <v>5.4</v>
       </c>
-      <c r="T66" s="31">
+      <c r="T66" s="32">
         <v>5.63</v>
       </c>
-      <c r="U66" s="31">
+      <c r="U66" s="32">
         <v>4.5</v>
       </c>
-      <c r="V66" s="31">
+      <c r="V66" s="32">
         <v>3.95</v>
       </c>
-      <c r="W66" s="31">
+      <c r="W66" s="32">
         <v>6.71</v>
       </c>
-      <c r="X66" s="31">
+      <c r="X66" s="32">
         <v>7.45</v>
       </c>
-      <c r="Y66" s="30"/>
-      <c r="Z66" s="30"/>
-      <c r="AA66" s="30"/>
-      <c r="AB66" s="30"/>
+      <c r="Y66" s="31"/>
+      <c r="Z66" s="31"/>
+      <c r="AA66" s="31"/>
+      <c r="AB66" s="31"/>
     </row>
     <row r="67" ht="15.0" customHeight="1">
-      <c r="A67" s="26" t="s">
-        <v>513</v>
-      </c>
-      <c r="B67" s="27"/>
-      <c r="C67" s="27"/>
-      <c r="D67" s="27"/>
-      <c r="E67" s="27"/>
-      <c r="F67" s="27"/>
-      <c r="G67" s="27"/>
-      <c r="H67" s="27"/>
-      <c r="I67" s="27"/>
-      <c r="J67" s="27"/>
-      <c r="K67" s="27"/>
-      <c r="L67" s="27"/>
-      <c r="M67" s="27"/>
-      <c r="N67" s="27"/>
-      <c r="O67" s="27"/>
-      <c r="P67" s="27"/>
-      <c r="Q67" s="27"/>
-      <c r="R67" s="27"/>
-      <c r="S67" s="27"/>
-      <c r="T67" s="27"/>
-      <c r="U67" s="27"/>
-      <c r="V67" s="27"/>
-      <c r="W67" s="27"/>
-      <c r="X67" s="27"/>
-      <c r="Y67" s="27"/>
-      <c r="Z67" s="27"/>
-      <c r="AA67" s="27"/>
-      <c r="AB67" s="27"/>
+      <c r="A67" s="27" t="s">
+        <v>516</v>
+      </c>
+      <c r="B67" s="28"/>
+      <c r="C67" s="28"/>
+      <c r="D67" s="28"/>
+      <c r="E67" s="28"/>
+      <c r="F67" s="28"/>
+      <c r="G67" s="28"/>
+      <c r="H67" s="28"/>
+      <c r="I67" s="28"/>
+      <c r="J67" s="28"/>
+      <c r="K67" s="28"/>
+      <c r="L67" s="28"/>
+      <c r="M67" s="28"/>
+      <c r="N67" s="28"/>
+      <c r="O67" s="28"/>
+      <c r="P67" s="28"/>
+      <c r="Q67" s="28"/>
+      <c r="R67" s="28"/>
+      <c r="S67" s="28"/>
+      <c r="T67" s="28"/>
+      <c r="U67" s="28"/>
+      <c r="V67" s="28"/>
+      <c r="W67" s="28"/>
+      <c r="X67" s="28"/>
+      <c r="Y67" s="28"/>
+      <c r="Z67" s="28"/>
+      <c r="AA67" s="28"/>
+      <c r="AB67" s="28"/>
     </row>
     <row r="68" ht="15.0" customHeight="1">
-      <c r="A68" s="28" t="s">
-        <v>514</v>
-      </c>
-      <c r="B68" s="31">
+      <c r="A68" s="29" t="s">
+        <v>517</v>
+      </c>
+      <c r="B68" s="32">
         <v>11.08</v>
       </c>
-      <c r="C68" s="31">
+      <c r="C68" s="32">
         <v>5.5</v>
       </c>
-      <c r="D68" s="31">
+      <c r="D68" s="32">
         <v>6.0</v>
       </c>
-      <c r="E68" s="31">
+      <c r="E68" s="32">
         <v>11.1</v>
       </c>
-      <c r="F68" s="31">
+      <c r="F68" s="32">
         <v>6.66</v>
       </c>
-      <c r="G68" s="31">
+      <c r="G68" s="32">
         <v>8.31</v>
       </c>
-      <c r="H68" s="31">
+      <c r="H68" s="32">
         <v>21.22</v>
       </c>
-      <c r="I68" s="31">
+      <c r="I68" s="32">
         <v>24.46</v>
       </c>
-      <c r="J68" s="31">
+      <c r="J68" s="32">
         <v>21.98</v>
       </c>
-      <c r="K68" s="31">
+      <c r="K68" s="32">
         <v>13.46</v>
       </c>
-      <c r="L68" s="31">
+      <c r="L68" s="32">
         <v>12.78</v>
       </c>
-      <c r="M68" s="31">
+      <c r="M68" s="32">
         <v>18.01</v>
       </c>
-      <c r="N68" s="31">
+      <c r="N68" s="32">
         <v>34.47</v>
       </c>
-      <c r="O68" s="31">
+      <c r="O68" s="32">
         <v>13.66</v>
       </c>
-      <c r="P68" s="31">
+      <c r="P68" s="32">
         <v>29.77</v>
       </c>
-      <c r="Q68" s="31">
+      <c r="Q68" s="32">
         <v>16.09</v>
       </c>
-      <c r="R68" s="31">
+      <c r="R68" s="32">
         <v>5.71</v>
       </c>
-      <c r="S68" s="31">
+      <c r="S68" s="32">
         <v>21.51</v>
       </c>
-      <c r="T68" s="31">
+      <c r="T68" s="32">
         <v>15.75</v>
       </c>
-      <c r="U68" s="31">
+      <c r="U68" s="32">
         <v>8.11</v>
       </c>
-      <c r="V68" s="31">
+      <c r="V68" s="32">
         <v>16.44</v>
       </c>
-      <c r="W68" s="31">
+      <c r="W68" s="32">
         <v>11.19</v>
       </c>
-      <c r="X68" s="31">
+      <c r="X68" s="32">
         <v>5.29</v>
       </c>
-      <c r="Y68" s="31">
+      <c r="Y68" s="32">
         <v>6.9</v>
       </c>
-      <c r="Z68" s="31">
+      <c r="Z68" s="32">
         <v>6.13</v>
       </c>
-      <c r="AA68" s="31">
+      <c r="AA68" s="32">
         <v>34.47</v>
       </c>
-      <c r="AB68" s="31">
+      <c r="AB68" s="32">
         <v>4.82</v>
       </c>
     </row>
     <row r="69" ht="15.0" customHeight="1">
-      <c r="A69" s="28" t="s">
-        <v>515</v>
-      </c>
-      <c r="B69" s="31">
+      <c r="A69" s="29" t="s">
+        <v>518</v>
+      </c>
+      <c r="B69" s="32">
         <v>7.5</v>
       </c>
-      <c r="C69" s="31">
+      <c r="C69" s="32">
         <v>7.24</v>
       </c>
-      <c r="D69" s="31">
+      <c r="D69" s="32">
         <v>8.79</v>
       </c>
-      <c r="E69" s="31">
+      <c r="E69" s="32">
         <v>11.11</v>
       </c>
-      <c r="F69" s="31">
+      <c r="F69" s="32">
         <v>12.14</v>
       </c>
-      <c r="G69" s="31">
+      <c r="G69" s="32">
         <v>15.11</v>
       </c>
-      <c r="H69" s="31">
+      <c r="H69" s="32">
         <v>18.14</v>
       </c>
-      <c r="I69" s="31">
+      <c r="I69" s="32">
         <v>17.47</v>
       </c>
-      <c r="J69" s="31">
+      <c r="J69" s="32">
         <v>17.79</v>
       </c>
-      <c r="K69" s="31">
+      <c r="K69" s="32">
         <v>16.13</v>
       </c>
-      <c r="L69" s="31">
+      <c r="L69" s="32">
         <v>18.66</v>
       </c>
-      <c r="M69" s="31">
+      <c r="M69" s="32">
         <v>20.07</v>
       </c>
-      <c r="N69" s="31">
+      <c r="N69" s="32">
         <v>15.1</v>
       </c>
-      <c r="O69" s="31">
+      <c r="O69" s="32">
         <v>13.7</v>
       </c>
-      <c r="P69" s="31">
+      <c r="P69" s="32">
         <v>14.05</v>
       </c>
-      <c r="Q69" s="31">
+      <c r="Q69" s="32">
         <v>10.86</v>
       </c>
-      <c r="R69" s="31">
+      <c r="R69" s="32">
         <v>10.51</v>
       </c>
-      <c r="S69" s="31">
+      <c r="S69" s="32">
         <v>13.09</v>
       </c>
-      <c r="T69" s="31">
+      <c r="T69" s="32">
         <v>10.32</v>
       </c>
-      <c r="U69" s="31">
+      <c r="U69" s="32">
         <v>8.73</v>
       </c>
-      <c r="V69" s="31">
+      <c r="V69" s="32">
         <v>8.5</v>
       </c>
-      <c r="W69" s="31">
+      <c r="W69" s="32">
         <v>10.75</v>
       </c>
-      <c r="X69" s="31">
+      <c r="X69" s="32">
         <v>9.9</v>
       </c>
-      <c r="Y69" s="30"/>
-      <c r="Z69" s="30"/>
-      <c r="AA69" s="30"/>
-      <c r="AB69" s="30"/>
+      <c r="Y69" s="31"/>
+      <c r="Z69" s="31"/>
+      <c r="AA69" s="31"/>
+      <c r="AB69" s="31"/>
     </row>
     <row r="70" ht="15.0" customHeight="1">
-      <c r="A70" s="26" t="s">
-        <v>516</v>
-      </c>
-      <c r="B70" s="27"/>
-      <c r="C70" s="27"/>
-      <c r="D70" s="27"/>
-      <c r="E70" s="27"/>
-      <c r="F70" s="27"/>
-      <c r="G70" s="27"/>
-      <c r="H70" s="27"/>
-      <c r="I70" s="27"/>
-      <c r="J70" s="27"/>
-      <c r="K70" s="27"/>
-      <c r="L70" s="27"/>
-      <c r="M70" s="27"/>
-      <c r="N70" s="27"/>
-      <c r="O70" s="27"/>
-      <c r="P70" s="27"/>
-      <c r="Q70" s="27"/>
-      <c r="R70" s="27"/>
-      <c r="S70" s="27"/>
-      <c r="T70" s="27"/>
-      <c r="U70" s="27"/>
-      <c r="V70" s="27"/>
-      <c r="W70" s="27"/>
-      <c r="X70" s="27"/>
-      <c r="Y70" s="27"/>
-      <c r="Z70" s="27"/>
-      <c r="AA70" s="27"/>
-      <c r="AB70" s="27"/>
+      <c r="A70" s="27" t="s">
+        <v>519</v>
+      </c>
+      <c r="B70" s="28"/>
+      <c r="C70" s="28"/>
+      <c r="D70" s="28"/>
+      <c r="E70" s="28"/>
+      <c r="F70" s="28"/>
+      <c r="G70" s="28"/>
+      <c r="H70" s="28"/>
+      <c r="I70" s="28"/>
+      <c r="J70" s="28"/>
+      <c r="K70" s="28"/>
+      <c r="L70" s="28"/>
+      <c r="M70" s="28"/>
+      <c r="N70" s="28"/>
+      <c r="O70" s="28"/>
+      <c r="P70" s="28"/>
+      <c r="Q70" s="28"/>
+      <c r="R70" s="28"/>
+      <c r="S70" s="28"/>
+      <c r="T70" s="28"/>
+      <c r="U70" s="28"/>
+      <c r="V70" s="28"/>
+      <c r="W70" s="28"/>
+      <c r="X70" s="28"/>
+      <c r="Y70" s="28"/>
+      <c r="Z70" s="28"/>
+      <c r="AA70" s="28"/>
+      <c r="AB70" s="28"/>
     </row>
     <row r="71" ht="15.0" customHeight="1">
-      <c r="A71" s="28" t="s">
-        <v>517</v>
-      </c>
-      <c r="B71" s="30"/>
-      <c r="C71" s="31">
+      <c r="A71" s="29" t="s">
+        <v>520</v>
+      </c>
+      <c r="B71" s="31"/>
+      <c r="C71" s="32">
         <v>8.32</v>
       </c>
-      <c r="D71" s="31">
+      <c r="D71" s="32">
         <v>8.02</v>
       </c>
-      <c r="E71" s="31">
+      <c r="E71" s="32">
         <v>17.28</v>
       </c>
-      <c r="F71" s="31">
+      <c r="F71" s="32">
         <v>7.48</v>
       </c>
-      <c r="G71" s="31">
+      <c r="G71" s="32">
         <v>9.26</v>
       </c>
-      <c r="H71" s="30"/>
-      <c r="I71" s="31">
+      <c r="H71" s="31"/>
+      <c r="I71" s="32">
         <v>31.65</v>
       </c>
-      <c r="J71" s="31">
+      <c r="J71" s="32">
         <v>31.78</v>
       </c>
-      <c r="K71" s="31">
+      <c r="K71" s="32">
         <v>17.29</v>
       </c>
-      <c r="L71" s="31">
+      <c r="L71" s="32">
         <v>61.9</v>
       </c>
-      <c r="M71" s="31">
+      <c r="M71" s="32">
         <v>23.34</v>
       </c>
-      <c r="N71" s="30"/>
-      <c r="O71" s="31">
+      <c r="N71" s="31"/>
+      <c r="O71" s="32">
         <v>36.3</v>
       </c>
-      <c r="P71" s="31">
+      <c r="P71" s="32">
         <v>38.15</v>
       </c>
-      <c r="Q71" s="31">
+      <c r="Q71" s="32">
         <v>17.96</v>
       </c>
-      <c r="R71" s="31">
+      <c r="R71" s="32">
         <v>15.84</v>
       </c>
-      <c r="S71" s="31">
+      <c r="S71" s="32">
         <v>34.97</v>
       </c>
-      <c r="T71" s="31">
+      <c r="T71" s="32">
         <v>26.61</v>
       </c>
-      <c r="U71" s="31">
+      <c r="U71" s="32">
         <v>8.79</v>
       </c>
-      <c r="V71" s="31">
+      <c r="V71" s="32">
         <v>17.96</v>
       </c>
-      <c r="W71" s="30"/>
-      <c r="X71" s="31">
+      <c r="W71" s="31"/>
+      <c r="X71" s="32">
         <v>5.48</v>
       </c>
-      <c r="Y71" s="31">
+      <c r="Y71" s="32">
         <v>8.64</v>
       </c>
-      <c r="Z71" s="31">
+      <c r="Z71" s="32">
         <v>18.28</v>
       </c>
-      <c r="AA71" s="30"/>
-      <c r="AB71" s="30"/>
+      <c r="AA71" s="31"/>
+      <c r="AB71" s="31"/>
     </row>
     <row r="72" ht="15.0" customHeight="1">
-      <c r="A72" s="28" t="s">
-        <v>518</v>
-      </c>
-      <c r="B72" s="31">
+      <c r="A72" s="29" t="s">
+        <v>521</v>
+      </c>
+      <c r="B72" s="32">
         <v>12.58</v>
       </c>
-      <c r="C72" s="31">
+      <c r="C72" s="32">
         <v>9.41</v>
       </c>
-      <c r="D72" s="31">
+      <c r="D72" s="32">
         <v>13.58</v>
       </c>
-      <c r="E72" s="31">
+      <c r="E72" s="32">
         <v>17.85</v>
       </c>
-      <c r="F72" s="31">
+      <c r="F72" s="32">
         <v>19.47</v>
       </c>
-      <c r="G72" s="31">
+      <c r="G72" s="32">
         <v>28.97</v>
       </c>
-      <c r="H72" s="31">
+      <c r="H72" s="32">
         <v>70.68</v>
       </c>
-      <c r="I72" s="31">
+      <c r="I72" s="32">
         <v>27.67</v>
       </c>
-      <c r="J72" s="31">
+      <c r="J72" s="32">
         <v>59.08</v>
       </c>
-      <c r="K72" s="31">
+      <c r="K72" s="32">
         <v>64.64</v>
       </c>
-      <c r="L72" s="29">
+      <c r="L72" s="30">
         <v>131.28</v>
       </c>
-      <c r="M72" s="31">
+      <c r="M72" s="32">
         <v>75.7</v>
       </c>
-      <c r="N72" s="31">
+      <c r="N72" s="32">
         <v>74.56</v>
       </c>
-      <c r="O72" s="31">
+      <c r="O72" s="32">
         <v>26.22</v>
       </c>
-      <c r="P72" s="31">
+      <c r="P72" s="32">
         <v>24.44</v>
       </c>
-      <c r="Q72" s="31">
+      <c r="Q72" s="32">
         <v>16.94</v>
       </c>
-      <c r="R72" s="31">
+      <c r="R72" s="32">
         <v>16.83</v>
       </c>
-      <c r="S72" s="31">
+      <c r="S72" s="32">
         <v>30.85</v>
       </c>
-      <c r="T72" s="31">
+      <c r="T72" s="32">
         <v>20.03</v>
       </c>
-      <c r="U72" s="31">
+      <c r="U72" s="32">
         <v>16.08</v>
       </c>
-      <c r="V72" s="31">
+      <c r="V72" s="32">
         <v>25.35</v>
       </c>
-      <c r="W72" s="31">
+      <c r="W72" s="32">
         <v>52.62</v>
       </c>
-      <c r="X72" s="31">
+      <c r="X72" s="32">
         <v>40.29</v>
       </c>
-      <c r="Y72" s="30"/>
-      <c r="Z72" s="30"/>
-      <c r="AA72" s="30"/>
-      <c r="AB72" s="30"/>
+      <c r="Y72" s="31"/>
+      <c r="Z72" s="31"/>
+      <c r="AA72" s="31"/>
+      <c r="AB72" s="31"/>
     </row>
     <row r="73" ht="15.75" customHeight="1"/>
     <row r="74" ht="15.75" customHeight="1"/>
